--- a/docs/UW_Dashboard_Metrics_Inventory.xlsx
+++ b/docs/UW_Dashboard_Metrics_Inventory.xlsx
@@ -1,28 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-10410" yWindow="-16395" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Read me" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Glossary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. Making DSR + RBS agree" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. What we CAN build" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. New ideas" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. What we CAN'T build" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="1. Read me" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2. Glossary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="3. Making DSR + RBS agree" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="4. What we CAN build" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="5. New ideas" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="6. What we CAN'T build" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="7. Filters" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="8. Build tracker" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="9. Decisions &amp; questions" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,42 +35,42 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="001F3864"/>
+      <color rgb="FF1F3864"/>
       <sz val="16"/>
     </font>
     <font>
       <name val="Arial"/>
       <i val="1"/>
-      <color rgb="00595959"/>
+      <color rgb="FF595959"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="001F3864"/>
+      <color rgb="FF1F3864"/>
       <sz val="13"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00000000"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00000000"/>
+      <color rgb="FF000000"/>
       <sz val="10.5"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="001F3864"/>
+      <color rgb="FF1F3864"/>
       <sz val="10.5"/>
     </font>
     <font>
@@ -83,18 +85,18 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="001F3864"/>
+      <color rgb="FF1F3864"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00595959"/>
+      <color rgb="FF595959"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="001F3864"/>
+      <color rgb="FF1F3864"/>
       <sz val="12"/>
     </font>
     <font>
@@ -109,7 +111,21 @@
     <font>
       <name val="Arial"/>
       <i val="1"/>
-      <color rgb="00595959"/>
+      <color rgb="FF595959"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF595959"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <sz val="9.5"/>
     </font>
   </fonts>
@@ -122,31 +138,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
+        <fgColor rgb="FF1F3864"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E2F3"/>
+        <fgColor rgb="FFD9E2F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4E4"/>
+        <fgColor rgb="FFFCE4E4"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -156,23 +172,48 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -180,43 +221,33 @@
     <border>
       <left/>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -232,17 +263,12 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -253,29 +279,75 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -638,13 +710,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A50"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:A59"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
-    <col width="108" customWidth="1" min="1" max="1"/>
+    <col width="108" customWidth="1" style="23" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="20.65" customHeight="1" s="23">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>UW Productivity Dashboard — built from DSR + RBS</t>
@@ -658,7 +730,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="16.9" customHeight="1" s="23">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>1. The three reports Matt's original dashboard used</t>
@@ -686,49 +758,49 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="16.9" customHeight="1" s="23">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>2. Our decision (updated)</t>
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="25.5" customHeight="1" s="23">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>We are now building this dashboard from DSR AND RBS together. This closes most of the funnel gap from the first version of this plan.</t>
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="25.5" customHeight="1" s="23">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>We still do not have the HR file, and still don't know who owns it. So headcount still needs a stand-in — see point 5, which now uses a better stand-in than before, built from DSR.</t>
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="16.9" customHeight="1" s="23">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>3. Why using two reports together is trickier than it sounds</t>
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="38.25" customHeight="1" s="23">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>DSR and RBS were never designed to be queried side by side. They use different field names for the same idea, they don't always agree on which month a policy belongs to, and RBS can contain more than one row for a single policy. Left alone, this produces two numbers that both look right and don't match.</t>
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="25.5" customHeight="1" s="23">
       <c r="A15" s="4" t="inlineStr">
         <is>
           <t>So before we calculate anything, we agree ONE set of rules that both reports follow the same way. That rulebook is the new tab “3. Making DSR + RBS agree.” Every metric later in this workbook assumes those rules are already applied.</t>
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="16.9" customHeight="1" s="23">
       <c r="A17" s="3" t="inlineStr">
         <is>
           <t>4. What this gets us that the RBS-only version couldn't</t>
@@ -749,7 +821,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="25.5" customHeight="1" s="23">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>•  We can check DSR and RBS against each other every time we calculate something, to catch mistakes early. This is exactly how Matt's own team once caught a premium figure that was quietly 2-3% too low.</t>
@@ -763,14 +835,14 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="16.9" customHeight="1" s="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
           <t>5. Headcount — our local solution, stated plainly</t>
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="25.5" customHeight="1" s="23">
       <c r="A24" s="4" t="inlineStr">
         <is>
           <t>We still have no HR file. But with DSR in scope, we can build a meaningfully better stand-in than before. Two versions, both built from data we actually have:</t>
@@ -791,7 +863,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="25.5" customHeight="1" s="23">
       <c r="A27" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">     This is not something we invented from nothing: Matt's own build already uses exactly this idea (he calls it “roster heads”) as its fallback wherever real headcount isn't available for a slice of the business.</t>
@@ -812,7 +884,7 @@
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="38.25" customHeight="1" s="23">
       <c r="A30" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">     Since RBS is the report the company already treats as the trusted source (see tab 3), this is the steadier of the two to lead with when the two disagree. Roster underwriters is still worth keeping alongside it as broader context, since it's the only one that can see people who tried and didn't win.</t>
@@ -854,28 +926,28 @@
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="25.5" customHeight="1" s="23">
       <c r="A36" s="4" t="inlineStr">
         <is>
           <t>•  Because the denominator only ever includes people who were active, “premium per person” will always look a little better than the true figure — Version A less so than Version B, since it counts more people, but the bias never fully goes away.</t>
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="25.5" customHeight="1" s="23">
       <c r="A37" s="4" t="inlineStr">
         <is>
           <t>We label every figure that uses either stand-in clearly, and never call it “headcount” without saying which version and that it's a stand-in.</t>
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="16.9" customHeight="1" s="23">
       <c r="A39" s="3" t="inlineStr">
         <is>
           <t>6. What still needs the HR file, no matter what</t>
         </is>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="25.5" customHeight="1" s="23">
       <c r="A40" s="4" t="inlineStr">
         <is>
           <t>•  True employed headcount — an exact count of who was on payroll, regardless of whether they submitted or won anything that month.</t>
@@ -889,14 +961,14 @@
         </is>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="25.5" customHeight="1" s="23">
       <c r="A42" s="4" t="inlineStr">
         <is>
           <t>•  Agency Revenue and fee income are unrelated to any of this — the columns they need simply don't exist in the standard RBS report, DSR or no DSR, HR file or no HR file.</t>
         </is>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="16.9" customHeight="1" s="23">
       <c r="A44" s="3" t="inlineStr">
         <is>
           <t>7. How to use the rest of this workbook</t>
@@ -910,7 +982,7 @@
         </is>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="25.5" customHeight="1" s="23">
       <c r="A46" s="4" t="inlineStr">
         <is>
           <t>•  3. Making DSR + RBS agree — the filter rulebook: how the two reports are lined up so they agree, before any metric is calculated.</t>
@@ -938,10 +1010,66 @@
         </is>
       </c>
     </row>
-    <row r="50">
+    <row r="50" ht="25.5" customHeight="1" s="23">
       <c r="A50" s="4" t="inlineStr">
         <is>
+          <t>•  7. Filters — every filter on the dashboard, how it behaves, and how it compares with Matt's build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>•  8. Build tracker — where every rule and metric stands in the code, with today's figure on real data, so progress and unexpected changes are easy to spot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>•  9. Decisions &amp; questions — every judgement call behind the numbers: what's agreed, and what still needs someone to decide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
           <t>Every table uses the same three colours: green means safe to use as-is, amber means usable but read the note next to it, red means not available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>8. Where things stand (17 Sep 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>•  Every metric in tab 4 and every idea in tab 5 is now built and on the dashboard (tab 8).</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>•  The dashboard has Matt's filters except Product (needs his product mapping) and Role / Tenure (need the HR file) — shown greyed out with the reason (tab 7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>•  Every figure is shown against the same period last year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>•  10 questions are open and worth raising with Matt or the extract owners (tab 9).</t>
         </is>
       </c>
     </row>
@@ -956,14 +1084,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:B50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" style="23" min="1" max="1"/>
+    <col width="90" customWidth="1" style="23" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="28.05" customHeight="1" s="23">
       <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Term</t>
@@ -976,442 +1104,558 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>The three source reports</t>
         </is>
       </c>
-      <c r="B2" s="11" t="n"/>
+      <c r="B2" s="17" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>DSR</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>“Deal Submission Report.” Every risk that came to us, whether we won it or not.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>RBS</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>“Risk Booking Summary.” Only the risks we actually won (bound).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>HR file</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>The staff file: who worked where, and for how long. Still not available to us.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>The funnel (now available, from DSR)</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n"/>
+      <c r="B6" s="17" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Submission</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>A risk that came in, at any stage — win, lose, or still pending.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Quote</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>A submission we priced (whether or not it was then won).</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Bind</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>A risk we actually won and put on cover.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Q/S (Quote rate)</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Of everything that came in, what share did we price? = Quotes ÷ Submissions.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>B/Q (Bind / win rate)</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Of everything we priced, what share did we win? = Binds ÷ Quotes.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+    <row r="12" ht="26.25" customHeight="1" s="23">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>B/S (End-to-end win rate)</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Of everything that came in, what share did we win? = Binds ÷ Submissions.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Money and premium</t>
         </is>
       </c>
-      <c r="B13" s="11" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="B13" s="17" t="n"/>
+    </row>
+    <row r="14" ht="26.25" customHeight="1" s="23">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>GWP (Gross Written Premium)</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>The premium amount on a policy. “Agency Share GWP” is Mosaic's own slice of that premium, in US dollars.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>Bound Premium</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>The total premium on business we actually won, in scope.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>Deal size</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Average premium per bound risk. = Premium ÷ Number of binds.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Profitability and pricing</t>
         </is>
       </c>
-      <c r="B17" s="11" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="B17" s="17" t="n"/>
+    </row>
+    <row r="18" ht="26.25" customHeight="1" s="23">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>GELR (Gross Expected Loss Ratio)</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Our best estimate, at the time of pricing, of what share of the premium will be paid out in claims. Lower is better.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+    <row r="19" ht="26.25" customHeight="1" s="23">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>Commission / Brokerage</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>The share of premium paid away as commission — mostly to the broker who brought the deal.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+    <row r="20" ht="26.25" customHeight="1" s="23">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>UW Margin % (Underwriting Margin)</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>What's left of each premium dollar after expected claims and commission. = 1 − GELR − Commission.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+    <row r="21" ht="25.5" customHeight="1" s="23">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Rate Adequacy</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Are we charging enough, compared to plan? Above 100% means we're pricing above plan; below 100% means below plan.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+    <row r="22" ht="26.25" customHeight="1" s="23">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>RARC (Risk Adjusted Rate Change)</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>On a renewal, how much the price actually moved, once the risk itself is accounted for. 100% means the rate stayed flat.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+    <row r="23" ht="25.5" customHeight="1" s="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>Attachment point</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>The amount of loss that has to happen before this policy starts paying out. Only relevant on “Excess” layers (see below).</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>Limit / Exposure</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>The most this policy could ever pay out.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>How business is placed</t>
         </is>
       </c>
-      <c r="B25" s="11" t="n"/>
+      <c r="B25" s="17" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>Primary layer</t>
         </is>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>The first layer of cover on a risk — pays out first.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>Excess layer</t>
         </is>
       </c>
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>A layer that only pays out after the primary layer (and any attachment point) is used up.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+    <row r="28" ht="26.25" customHeight="1" s="23">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>MOP (Method of Placement)</t>
         </is>
       </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>How the business reached us — e.g. “Open Market” (brokered case by case) vs. “Facility/DUA” (pre-agreed delegated authority).</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>Slip Lead</t>
         </is>
       </c>
-      <c r="B29" s="10" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>Who is steering the terms on a shared placement. “Mosaic as Lead” = how often that's us.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+    <row r="30" ht="26.25" customHeight="1" s="23">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>SCM (Syndicate Capital Management) Share</t>
         </is>
       </c>
-      <c r="B30" s="10" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>The share of premium sitting on someone else's balance sheet (third-party capital) rather than Mosaic's own.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+    <row r="31" ht="25.5" customHeight="1" s="23">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>New vs. Renewal</t>
         </is>
       </c>
-      <c r="B31" s="10" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>Whether a policy is a brand-new client relationship or a repeat of one from last year. DSR and RBS record this slightly differently — see tab 3.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>People and productivity</t>
         </is>
       </c>
-      <c r="B32" s="11" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="B32" s="17" t="n"/>
+    </row>
+    <row r="33" ht="25.5" customHeight="1" s="23">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>Heads / Headcount</t>
         </is>
       </c>
-      <c r="B33" s="10" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>How many people were actually employed as underwriters, on average, over a period. Comes from the HR file — still not available here.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+    <row r="34" ht="39.4" customHeight="1" s="23">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>Active underwriters (our recommended stand-in for Heads)</t>
         </is>
       </c>
-      <c r="B34" s="10" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>Every different underwriter who won at least one deal in the period. Built from RBS, our source of truth for bound business. See “1. Read me”, point 5.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+    <row r="35" ht="39.4" customHeight="1" s="23">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>Roster underwriters (a broader, secondary stand-in)</t>
         </is>
       </c>
-      <c r="B35" s="10" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>Every different underwriter with at least one submission in the period, win or not. Built from DSR. See “1. Read me”, point 5.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="9" t="inlineStr">
+    <row r="36" ht="25.5" customHeight="1" s="23">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>Premium / head</t>
         </is>
       </c>
-      <c r="B36" s="10" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>Bound premium divided by headcount (or, here, by one of our two stand-ins). The dashboard's main productivity measure.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+    <row r="37" ht="25.5" customHeight="1" s="23">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>Role / Tenure</t>
         </is>
       </c>
-      <c r="B37" s="10" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>Whether someone is an underwriter or in leadership, and how long they've been at Mosaic. Comes from the HR file — not available here.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>Agency Revenue (not available — the source columns don't exist)</t>
         </is>
       </c>
-      <c r="B38" s="11" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="B38" s="17" t="n"/>
+    </row>
+    <row r="39" ht="25.5" customHeight="1" s="23">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>Agency Revenue</t>
         </is>
       </c>
-      <c r="B39" s="10" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>Fee income earned on the business, separate from the underwriting margin. Needs columns that don't exist in the standard RBS report.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>Fee Yield</t>
         </is>
       </c>
-      <c r="B40" s="10" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t>Fee income as a share of premium.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>Filters and time windows (see tab 7)</t>
+        </is>
+      </c>
+      <c r="B41" s="16" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>YTD (Year to date)</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>From January to the last complete month of the year, e.g. Jan-Aug 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>TTM (Trailing twelve months)</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>The twelve months ending with the last complete month, e.g. Sep 2025-Aug 2026. Smooths out seasonal swings that a YTD view can't.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>Last complete month</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>The latest month with a full month of data behind it. The month still in progress is marked with an orange dot, because its figures are still filling in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>Prior year / comparison</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>The same months one year earlier. Every figure is shown next to it, with the change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>pts (percentage points)</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>How a percentage moves: 42.0% to 44.0% is +2.0 pts (not +4.8%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>Date basis</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>Which date puts a policy in a month: inception (when cover starts) or submission (when it came in). Submission basis only works for DSR figures - RBS has no submission date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>Cascading filter</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>A dropdown that only offers choices that exist under the other filters you've picked, so you never pick your way to an empty page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>Peer median</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>The middle premium among the underwriters in the current filters (leaving out those with none). "1.5x" means 50% more premium than that middle figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>Median</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>The middle value when sorted. Used instead of an average where a few huge values would distort it - attachment points, limits.</t>
         </is>
       </c>
     </row>
@@ -1436,57 +1680,56 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D48"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" style="23" min="1" max="1"/>
+    <col width="26" customWidth="1" style="23" min="2" max="3"/>
+    <col width="60" customWidth="1" style="23" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+    <row r="1" ht="17.65" customHeight="1" s="23">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>The rulebook: how DSR and RBS are lined up so they agree</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+    <row r="2" ht="216.75" customHeight="1" s="23">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>DSR and RBS were built separately and were never designed to be queried together. Applied carelessly, the same-looking question (“what was our premium in June?”) can get two different, both-plausible answers depending on which report you asked. This tab is the fix: one shared rulebook, applied the same way every time, so the two reports are compared like-for-like instead of by accident.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+    <row r="4" ht="45" customHeight="1" s="23">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Rule 1 — One shared definition of “in scope”</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="267.75" customHeight="1" s="23">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Every question we ask (which year, which months, which entity, which line of business, New vs. Renewal, which placement type) is written down ONCE, as a single set of conditions. Both DSR and RBS are then filtered using that exact same set of conditions — never two separate, hand-written versions of the same filter that could quietly drift apart. This is the single most common source of mismatches in Matt's own build, by his own account, so it's worth getting right from day one rather than fixing later.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+    <row r="8" ht="60" customHeight="1" s="23">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Rule 2 — The same idea, different field names: a translation table</t>
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="89.25" customHeight="1" s="23">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>DSR and RBS often store the same idea under a different column name, or a slightly different definition. Below is the translation we'll use everywhere.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="28" customHeight="1">
+    <row r="11" ht="28.05" customHeight="1" s="23">
       <c r="A11" s="6" t="inlineStr">
         <is>
           <t>What we mean</t>
@@ -1509,293 +1752,293 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Line of business</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>Class Of Business</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>Class of Business</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>Same idea, different capital letters only. Treat as identical.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+    <row r="13" ht="34.9" customHeight="1" s="23">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>New vs. Renewal</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>Business Type (“New” / “Renewal”)</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>Renewal Status (“New” / “Renewal”)</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>Two different fields, filled in separately. They usually agree, but not always for the same policy. When they disagree, we follow RBS's Renewal Status — see the note on Rule 6.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+    <row r="14" ht="23.25" customHeight="1" s="23">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Placement type</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>Mapped Method of Placement (MOP)</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>Mapped Method of Placement (MOP)</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>Same field name, no catch.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+    <row r="15" ht="23.25" customHeight="1" s="23">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Which underwriter gets credit</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>Producing Underwriter Name, else Underwriter Name</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>Producing Underwriter Name, else Underwriter Name</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>Same rule on both sides, so this stays consistent — see Rule 5 for the harder part (name spelling).</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>Which entity wrote it</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>Producing Mosaic Entity</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>Producing Mosaic Entity</t>
         </is>
       </c>
-      <c r="D16" s="15" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>Same field, same clean-up rule applied to both sides.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+    <row r="17" ht="23.25" customHeight="1" s="23">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>When the policy started</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>Inception date (or Submission Date)</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>Inception Date only</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>RBS has no submission date at all. See Rule 3.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+    <row r="18" ht="34.9" customHeight="1" s="23">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Was it won?</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>XFI Policy Status (several possible values)</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>n/a — every RBS row is already a win</t>
         </is>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>We use one, agreed list of “won” statuses on the DSR side, matching what actually ends up in RBS, so a DSR “Bind” count and an RBS row count describe the same thing.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+    <row r="20" ht="30" customHeight="1" s="23">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Rule 3 — Which date to trust</t>
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="63.75" customHeight="1" s="23">
       <c r="A21" s="4" t="inlineStr">
         <is>
           <t>RBS only ever records the inception date — there is no submission date on the RBS side at all. So:</t>
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="89.25" customHeight="1" s="23">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>•  Whenever we're combining figures from both reports (for example, Premium vs. Win rate in the same view), we always use INCEPTION date on both sides.</t>
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="191.25" customHeight="1" s="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
           <t>•  A “Submission date” view is only ever possible for DSR-only figures (Submissions, Quotes, the funnel) — the moment a quality figure from RBS (GELR, Margin, Commission) needs to join that view, we're silently mixing two different months. We won't do this — any submission-basis view will be clearly labelled as DSR-only.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="14" t="inlineStr">
+    <row r="25" ht="45" customHeight="1" s="23">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Rule 4 — Counting a policy once, not once per line</t>
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="140.25" customHeight="1" s="23">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>A single policy can have more than one row in either report (for example, several coverage lines under one policy). Two mistakes are easy to make here, and Matt's own build has a documented case of the first one costing real money:</t>
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="178.5" customHeight="1" s="23">
       <c r="A27" s="4" t="inlineStr">
         <is>
           <t>•  Mistake: adding up premium AFTER collapsing to one row per policy. This quietly lost 1.9–2.8% of premium in Matt's build for weeks, and every internal check still passed while it happened, because the mistake doesn't show up as an error — it just produces a slightly smaller, still-plausible number.</t>
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="114.75" customHeight="1" s="23">
       <c r="A28" s="4" t="inlineStr">
         <is>
           <t>•  Our rule: always add up premium ACROSS every line of a policy FIRST. Only after that do we collapse down to one row per policy, for counting purposes (how many distinct policies, not how many lines).</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="14" t="inlineStr">
+    <row r="30" ht="60" customHeight="1" s="23">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>Rule 5 — Underwriter name spelling (a genuine, open limitation)</t>
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="140.25" customHeight="1" s="23">
       <c r="A31" s="4" t="inlineStr">
         <is>
           <t>The same underwriter sometimes appears under two different spellings in the raw data (for example, a typo that stuck). Matt's build fixes this using a hand-maintained matching table that lives inside the HR file — which we don't have.</t>
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="178.5" customHeight="1" s="23">
       <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Our workaround: we clean up obvious formatting differences automatically (capital letters, punctuation, extra spaces) so the easy cases are caught. But a genuine spelling difference (like a name typed two different ways) will NOT be caught without a hand-built list, which we don't currently have the source for.</t>
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="140.25" customHeight="1" s="23">
       <c r="A33" s="4" t="inlineStr">
         <is>
           <t>This means a small number of underwriters could appear as two separate people in our results. Worth flagging to whoever reviews underwriter-level figures, and worth building a short manual list by hand if a review turns up any obvious duplicates.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="14" t="inlineStr">
+    <row r="35" ht="75" customHeight="1" s="23">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>Rule 6 — Check the two reports against each other, and know which one wins</t>
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="89.25" customHeight="1" s="23">
       <c r="A36" s="4" t="inlineStr">
         <is>
           <t>For any period and scope, we calculate bound premium TWO ways — once counting bound rows in DSR, once summing RBS directly — and compare them.</t>
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="76.5" customHeight="1" s="23">
       <c r="A37" s="4" t="inlineStr">
         <is>
           <t>•  Close match (a small gap, a percent or two) — expected and fine; the two reports are built slightly differently and will rarely be pixel-perfect.</t>
         </is>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="89.25" customHeight="1" s="23">
       <c r="A38" s="4" t="inlineStr">
         <is>
           <t>•  A bigger gap — a signal, not a bug to hide. It usually means the scope isn't lined up the same way on both sides (Rules 1–4), and it's worth chasing down.</t>
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="280.5" customHeight="1" s="23">
       <c r="A39" s="4" t="inlineStr">
         <is>
           <t>When they genuinely disagree and we have to pick one: RBS wins. This isn't a technical judgement — it's simply how the company already treats these two reports today. RBS is the established source of truth for bound business; DSR has not been described to us the same way. So DSR is the only place to get funnel figures (Submissions, Quotes, win rates) that RBS cannot provide at all, but wherever the two reports both speak to the same fact about bound business, RBS's figure is the one we keep.</t>
         </is>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="127.5" customHeight="1" s="23">
       <c r="A40" s="4" t="inlineStr">
         <is>
           <t>This still mirrors the useful idea from the original prototype — using two independent sources to catch mistakes — it just also says clearly who wins when they don't agree, rather than leaving that undecided.</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="14" t="inlineStr">
+    <row r="42" ht="60" customHeight="1" s="23">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>Rule 7 — Which report is the source of truth for which metric</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="28" customHeight="1">
+    <row r="43" ht="28.05" customHeight="1" s="23">
       <c r="A43" s="6" t="inlineStr">
         <is>
           <t>Metric</t>
@@ -1812,86 +2055,86 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="15" t="inlineStr">
+    <row r="44" ht="34.9" customHeight="1" s="23">
+      <c r="A44" s="12" t="inlineStr">
         <is>
           <t>Submissions, Quotes, Q/S, B/Q, B/S</t>
         </is>
       </c>
-      <c r="B44" s="15" t="inlineStr">
+      <c r="B44" s="12" t="inlineStr">
         <is>
           <t>DSR</t>
         </is>
       </c>
-      <c r="C44" s="15" t="inlineStr">
+      <c r="C44" s="12" t="inlineStr">
         <is>
           <t>Only DSR contains anything that wasn't won. RBS has no opinion here at all.</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="15" t="inlineStr">
+    <row r="45" ht="81.40000000000001" customHeight="1" s="23">
+      <c r="A45" s="12" t="inlineStr">
         <is>
           <t>Binds (count of won risks)</t>
         </is>
       </c>
-      <c r="B45" s="15" t="inlineStr">
+      <c r="B45" s="12" t="inlineStr">
         <is>
           <t>RBS, cross-checked against DSR's bind count (Rule 6)</t>
         </is>
       </c>
-      <c r="C45" s="15" t="inlineStr">
+      <c r="C45" s="12" t="inlineStr">
         <is>
           <t>Every RBS row is already a bound risk, and RBS is the company's established source of truth for bound business. DSR's own bind count is used as a cross-check, not the primary figure.</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="15" t="inlineStr">
+    <row r="46" ht="93" customHeight="1" s="23">
+      <c r="A46" s="12" t="inlineStr">
         <is>
           <t>Headline Bound Premium</t>
         </is>
       </c>
-      <c r="B46" s="15" t="inlineStr">
+      <c r="B46" s="12" t="inlineStr">
         <is>
           <t>RBS's own premium field, cross-checked against DSR's bound rows (Rule 6)</t>
         </is>
       </c>
-      <c r="C46" s="15" t="inlineStr">
+      <c r="C46" s="12" t="inlineStr">
         <is>
           <t>Same reasoning as Binds — RBS is treated as correct for bound business. Matt's original build actually did this the other way round (DSR as primary); we're deliberately changing that to match how the company actually treats these reports.</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="15" t="inlineStr">
+    <row r="47" ht="46.5" customHeight="1" s="23">
+      <c r="A47" s="12" t="inlineStr">
         <is>
           <t>GELR, Commission, UW Margin %, Rate Adequacy, RARC, fees (if ever available)</t>
         </is>
       </c>
-      <c r="B47" s="15" t="inlineStr">
+      <c r="B47" s="12" t="inlineStr">
         <is>
           <t>RBS</t>
         </is>
       </c>
-      <c r="C47" s="15" t="inlineStr">
+      <c r="C47" s="12" t="inlineStr">
         <is>
           <t>This detail doesn't exist in DSR at all.</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="15" t="inlineStr">
+    <row r="48" ht="104.65" customHeight="1" s="23">
+      <c r="A48" s="12" t="inlineStr">
         <is>
           <t>Headcount stand-ins (Roster / Active underwriters)</t>
         </is>
       </c>
-      <c r="B48" s="15" t="inlineStr">
+      <c r="B48" s="12" t="inlineStr">
         <is>
           <t>Active (RBS) is the steadier of the two; Roster (DSR) is supplementary</t>
         </is>
       </c>
-      <c r="C48" s="15" t="inlineStr">
+      <c r="C48" s="12" t="inlineStr">
         <is>
           <t>Active underwriters is built entirely from RBS, so it inherits RBS's status as the more trusted report. Roster underwriters still needs DSR, since submissions that weren't won only exist there — use it for context, lean on Active where the two disagree.</t>
         </is>
@@ -1908,38 +2151,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" style="23" min="1" max="1"/>
+    <col width="32" customWidth="1" style="23" min="2" max="2"/>
+    <col width="36" customWidth="1" style="23" min="3" max="3"/>
+    <col width="16" customWidth="1" style="23" min="4" max="4"/>
+    <col width="13" customWidth="1" style="23" min="5" max="5"/>
+    <col width="46" customWidth="1" style="23" min="6" max="6"/>
+    <col width="20" customWidth="1" style="23" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="23">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>Green = fully OK to use</t>
         </is>
       </c>
-      <c r="B1" s="11" t="n"/>
-      <c r="C1" s="17" t="inlineStr">
+      <c r="B1" s="17" t="n"/>
+      <c r="C1" s="19" t="inlineStr">
         <is>
           <t>Amber = OK, but read the note</t>
         </is>
       </c>
-      <c r="D1" s="11" t="n"/>
-      <c r="E1" s="18" t="inlineStr">
+      <c r="D1" s="17" t="n"/>
+      <c r="E1" s="20" t="inlineStr">
         <is>
           <t>Red = not available</t>
         </is>
       </c>
-      <c r="F1" s="11" t="n"/>
-    </row>
-    <row r="2" ht="30" customHeight="1">
+      <c r="F1" s="17" t="n"/>
+    </row>
+    <row r="2" ht="30" customHeight="1" s="23">
       <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Metric</t>
@@ -1970,1040 +2214,1207 @@
           <t>Note / catch</t>
         </is>
       </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>Built? (17 Sep 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>THE FUNNEL (now available, from DSR)</t>
         </is>
       </c>
-      <c r="B3" s="21" t="n"/>
-      <c r="C3" s="21" t="n"/>
-      <c r="D3" s="21" t="n"/>
-      <c r="E3" s="21" t="n"/>
-      <c r="F3" s="11" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="B3" s="18" t="n"/>
+      <c r="C3" s="18" t="n"/>
+      <c r="D3" s="18" t="n"/>
+      <c r="E3" s="18" t="n"/>
+      <c r="F3" s="17" t="n"/>
+      <c r="G3" s="25" t="n"/>
+    </row>
+    <row r="4" ht="23.25" customHeight="1" s="23">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Submissions</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>How many risks came to us in total, won or not.</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>Count distinct policies with any status, in scope.</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>DSR</t>
         </is>
       </c>
-      <c r="E4" s="19" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="F4" s="12" t="n"/>
+      <c r="G4" s="26" t="inlineStr">
+        <is>
+          <t>Built - see tab 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="23.25" customHeight="1" s="23">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Quotes</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>How many risks we priced.</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>Count distinct policies with a quoted status, in scope.</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>DSR</t>
         </is>
       </c>
-      <c r="E5" s="19" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F5" s="15" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="26" t="inlineStr">
+        <is>
+          <t>Built - see tab 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34.9" customHeight="1" s="23">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Binds</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>How many risks we won.</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>Count distinct policies with a bound RBS row — RBS is our source of truth for bound business.</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>RBS, cross-checked against DSR</t>
         </is>
       </c>
-      <c r="E6" s="19" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>DSR's own bind count is used only as a cross-check (tab 3, Rule 6), not the primary figure — RBS wins if the two disagree.</t>
         </is>
       </c>
+      <c r="G6" s="26" t="inlineStr">
+        <is>
+          <t>Built - see tab 8</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Q/S (Quote rate)</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>Share of what came in that we priced.</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>Quotes ÷ Submissions</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>DSR</t>
         </is>
       </c>
-      <c r="E7" s="19" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F7" s="15" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>Blank (not zero) if there were no submissions.</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="G7" s="26" t="inlineStr">
+        <is>
+          <t>Built - see tab 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34.9" customHeight="1" s="23">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>B/Q (Win rate)</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>Share of what we priced that we won.</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>Binds (RBS) ÷ Quotes (DSR)</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>DSR + RBS</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F8" s="15" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t>Blank (not zero) if there were no quotes. Mixes the two reports on purpose — Binds now comes from RBS, our source of truth for bound business.</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="G8" s="26" t="inlineStr">
+        <is>
+          <t>Built - see tab 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="23.25" customHeight="1" s="23">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>B/S (End-to-end win rate)</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>Share of everything that came in that we won.</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>Binds (RBS) ÷ Submissions (DSR) = Q/S × B/Q</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>DSR + RBS</t>
         </is>
       </c>
-      <c r="E9" s="19" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t>Same mixed-source note as B/Q above.</t>
         </is>
       </c>
+      <c r="G9" s="26" t="inlineStr">
+        <is>
+          <t>Built - see tab 8</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>HOW MUCH WE WROTE</t>
         </is>
       </c>
-      <c r="B10" s="21" t="n"/>
-      <c r="C10" s="21" t="n"/>
-      <c r="D10" s="21" t="n"/>
-      <c r="E10" s="21" t="n"/>
-      <c r="F10" s="11" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="B10" s="18" t="n"/>
+      <c r="C10" s="18" t="n"/>
+      <c r="D10" s="18" t="n"/>
+      <c r="E10" s="18" t="n"/>
+      <c r="F10" s="17" t="n"/>
+      <c r="G10" s="25" t="n"/>
+    </row>
+    <row r="11" ht="58.15" customHeight="1" s="23">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Bound Premium (GWP)</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>Total premium on business we won.</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>Add up the premium on every RBS row — RBS is our source of truth for bound business — cross-checked against the DSR bound-row total for the same scope (summed per policy line first, see tab 3, Rule 4).</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>RBS, checked against DSR</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>The two won't always match exactly — a small gap is expected (tab 3, Rule 6). If they disagree by more than a little, RBS's figure is the one we keep.</t>
         </is>
       </c>
+      <c r="G11" s="26" t="inlineStr">
+        <is>
+          <t>Built - see tab 8</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Average Deal Size</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>The average size of a won policy.</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>Bound Premium ÷ Binds.</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>RBS</t>
         </is>
       </c>
-      <c r="E12" s="19" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F12" s="15" t="inlineStr"/>
+      <c r="F12" s="12" t="n"/>
+      <c r="G12" s="26" t="inlineStr">
+        <is>
+          <t>Built - see tab 8</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>HOW GOOD THE BUSINESS IS (RBS's strongest area)</t>
         </is>
       </c>
-      <c r="B13" s="21" t="n"/>
-      <c r="C13" s="21" t="n"/>
-      <c r="D13" s="21" t="n"/>
-      <c r="E13" s="21" t="n"/>
-      <c r="F13" s="11" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="B13" s="18" t="n"/>
+      <c r="C13" s="18" t="n"/>
+      <c r="D13" s="18" t="n"/>
+      <c r="E13" s="18" t="n"/>
+      <c r="F13" s="17" t="n"/>
+      <c r="G13" s="25" t="n"/>
+    </row>
+    <row r="14" ht="23.25" customHeight="1" s="23">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>GELR</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>Our estimate of what share of premium will be paid out in claims.</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>Average GELR, weighted by premium size, across all rows.</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>RBS</t>
         </is>
       </c>
-      <c r="E14" s="19" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F14" s="15" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="F14" s="12" t="n"/>
+      <c r="G14" s="27" t="inlineStr">
+        <is>
+          <t>Built - read note - see tab 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="46.5" customHeight="1" s="23">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>GELR (margin version)</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>The same idea, but only counting rows that have a usable GELR figure — exactly the rows the margin below is built from.</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>Same average, but only over usable rows.</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>RBS</t>
         </is>
       </c>
-      <c r="E15" s="19" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F15" s="15" t="inlineStr">
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>Matt's build sometimes shows both versions of GELR under the same label, which is confusing. We'll always say clearly which one we mean.</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="G15" s="26" t="inlineStr">
+        <is>
+          <t>Built - see tab 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="23.25" customHeight="1" s="23">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>Commission</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>The share of premium paid away, mostly to brokers.</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>Average commission, weighted by premium size, across all rows.</t>
         </is>
       </c>
-      <c r="D16" s="15" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>RBS</t>
         </is>
       </c>
-      <c r="E16" s="19" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F16" s="15" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="F16" s="12" t="n"/>
+      <c r="G16" s="26" t="inlineStr">
+        <is>
+          <t>Built - see tab 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="23.25" customHeight="1" s="23">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>Commission (margin version)</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>The same idea, restricted to the rows the margin uses.</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>Same, restricted to usable rows.</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>RBS</t>
         </is>
       </c>
-      <c r="E17" s="19" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F17" s="15" t="inlineStr">
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>Same both-versions note as GELR above.</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="G17" s="26" t="inlineStr">
+        <is>
+          <t>Built - see tab 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34.9" customHeight="1" s="23">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>UW Margin %</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>What's left of each premium dollar after claims and commission.</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>1 minus GELR minus Commission.</t>
         </is>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>RBS</t>
         </is>
       </c>
-      <c r="E18" s="19" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F18" s="15" t="inlineStr">
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>Open question, never settled in Matt's build either: should this also subtract Mosaic's own internal commission? Worth a fresh decision, not copying the old one.</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="G18" s="27" t="inlineStr">
+        <is>
+          <t>Built - read note - see tab 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="23.25" customHeight="1" s="23">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>Margin cover</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>How much of our premium the Margin % figure is actually based on.</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>Share of premium that has a usable GELR.</t>
         </is>
       </c>
-      <c r="D19" s="15" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>RBS</t>
         </is>
       </c>
-      <c r="E19" s="19" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F19" s="15" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="F19" s="12" t="n"/>
+      <c r="G19" s="26" t="inlineStr">
+        <is>
+          <t>Built - see tab 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="23.25" customHeight="1" s="23">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>Commission cover</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>How much of the margin premium has a recorded commission.</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>Share with commission above zero.</t>
         </is>
       </c>
-      <c r="D20" s="15" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>RBS</t>
         </is>
       </c>
-      <c r="E20" s="19" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F20" s="15" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="F20" s="12" t="n"/>
+      <c r="G20" s="26" t="inlineStr">
+        <is>
+          <t>Built - see tab 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="23.25" customHeight="1" s="23">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>Attachment point (Excess)</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>The typical loss level before an excess policy starts paying.</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>Middle value (median), Excess layers only.</t>
         </is>
       </c>
-      <c r="D21" s="15" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>RBS</t>
         </is>
       </c>
-      <c r="E21" s="19" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F21" s="15" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="F21" s="12" t="n"/>
+      <c r="G21" s="26" t="inlineStr">
+        <is>
+          <t>Built - see tab 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="34.9" customHeight="1" s="23">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>Attachment point (Primary)</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>The typical loss level before a primary policy starts paying.</t>
         </is>
       </c>
-      <c r="C22" s="15" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>Middle value (median), Primary layers only.</t>
         </is>
       </c>
-      <c r="D22" s="15" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
         <is>
           <t>RBS</t>
         </is>
       </c>
-      <c r="E22" s="19" t="inlineStr">
+      <c r="E22" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F22" s="15" t="inlineStr">
+      <c r="F22" s="12" t="inlineStr">
         <is>
           <t>Often understated: many rows are missing a deductible value, and a blank is treated as zero. Same issue Matt's build has.</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="G22" s="27" t="inlineStr">
+        <is>
+          <t>Built - read note - see tab 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="34.9" customHeight="1" s="23">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>Average Limit</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>The typical size of cover we're on the hook for.</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>Middle value (median) of Agency Exposure.</t>
         </is>
       </c>
-      <c r="D23" s="15" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
         <is>
           <t>RBS</t>
         </is>
       </c>
-      <c r="E23" s="19" t="inlineStr">
+      <c r="E23" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F23" s="15" t="inlineStr">
+      <c r="F23" s="12" t="inlineStr">
         <is>
           <t>Called “Average” in Matt's build, but it's really a middle value (median), not a true average. We'll name it correctly from the start.</t>
         </is>
       </c>
+      <c r="G23" s="26" t="inlineStr">
+        <is>
+          <t>Built - see tab 8</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>PRICING</t>
         </is>
       </c>
-      <c r="B24" s="21" t="n"/>
-      <c r="C24" s="21" t="n"/>
-      <c r="D24" s="21" t="n"/>
-      <c r="E24" s="21" t="n"/>
-      <c r="F24" s="11" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="B24" s="18" t="n"/>
+      <c r="C24" s="18" t="n"/>
+      <c r="D24" s="18" t="n"/>
+      <c r="E24" s="18" t="n"/>
+      <c r="F24" s="17" t="n"/>
+      <c r="G24" s="25" t="n"/>
+    </row>
+    <row r="25" ht="46.5" customHeight="1" s="23">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>Rate Adequacy</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>Are we charging enough compared to plan?</t>
         </is>
       </c>
-      <c r="C25" s="15" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>Actual premium ÷ the plan-based benchmark premium.</t>
         </is>
       </c>
-      <c r="D25" s="15" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>RBS</t>
         </is>
       </c>
-      <c r="E25" s="19" t="inlineStr">
+      <c r="E25" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F25" s="15" t="inlineStr">
+      <c r="F25" s="12" t="inlineStr">
         <is>
           <t>Matt's version compares against a benchmark that only includes some rows, which slightly overstates the result. We should either fix that, or check our number against RBS's own ready-made “Achieved Price” column.</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="G25" s="26" t="inlineStr">
+        <is>
+          <t>Built - see tab 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="23.25" customHeight="1" s="23">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>RARC</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>How much prices moved on renewals, once the risk itself is accounted for.</t>
         </is>
       </c>
-      <c r="C26" s="15" t="inlineStr">
+      <c r="C26" s="12" t="inlineStr">
         <is>
           <t>Weighted average rate change on renewing business only.</t>
         </is>
       </c>
-      <c r="D26" s="15" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>RBS</t>
         </is>
       </c>
-      <c r="E26" s="19" t="inlineStr">
+      <c r="E26" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F26" s="15" t="inlineStr">
+      <c r="F26" s="12" t="inlineStr">
         <is>
           <t>Always renewals only, no matter what other filters are set — same rule Matt used.</t>
         </is>
       </c>
+      <c r="G26" s="26" t="inlineStr">
+        <is>
+          <t>Built - see tab 8</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>WHAT KIND OF BOOK WE WRITE</t>
         </is>
       </c>
-      <c r="B27" s="21" t="n"/>
-      <c r="C27" s="21" t="n"/>
-      <c r="D27" s="21" t="n"/>
-      <c r="E27" s="21" t="n"/>
-      <c r="F27" s="11" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="B27" s="18" t="n"/>
+      <c r="C27" s="18" t="n"/>
+      <c r="D27" s="18" t="n"/>
+      <c r="E27" s="18" t="n"/>
+      <c r="F27" s="17" t="n"/>
+      <c r="G27" s="25" t="n"/>
+    </row>
+    <row r="28" ht="34.9" customHeight="1" s="23">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>Mosaic as Lead</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>How often we set the terms on a shared placement.</t>
         </is>
       </c>
-      <c r="C28" s="15" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
         <is>
           <t>Rows where we're the lead ÷ all rows.</t>
         </is>
       </c>
-      <c r="D28" s="15" t="inlineStr">
+      <c r="D28" s="12" t="inlineStr">
         <is>
           <t>RBS</t>
         </is>
       </c>
-      <c r="E28" s="19" t="inlineStr">
+      <c r="E28" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F28" s="15" t="inlineStr">
+      <c r="F28" s="12" t="inlineStr">
         <is>
           <t>This counts policy rows, not premium dollars — a small deal counts the same as a large one. Same limitation in Matt's build.</t>
         </is>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="G28" s="26" t="inlineStr">
+        <is>
+          <t>Built - see tab 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="23.25" customHeight="1" s="23">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>Primary Share</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>How much of our book is first-layer cover.</t>
         </is>
       </c>
-      <c r="C29" s="15" t="inlineStr">
+      <c r="C29" s="12" t="inlineStr">
         <is>
           <t>Primary rows ÷ all rows.</t>
         </is>
       </c>
-      <c r="D29" s="15" t="inlineStr">
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>RBS</t>
         </is>
       </c>
-      <c r="E29" s="19" t="inlineStr">
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F29" s="15" t="inlineStr">
+      <c r="F29" s="12" t="inlineStr">
         <is>
           <t>Same row-count caveat as above.</t>
         </is>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="G29" s="26" t="inlineStr">
+        <is>
+          <t>Built - see tab 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="23.25" customHeight="1" s="23">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t>Average Agency Share</t>
         </is>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>How big a slice of each placement we typically take.</t>
         </is>
       </c>
-      <c r="C30" s="15" t="inlineStr">
+      <c r="C30" s="12" t="inlineStr">
         <is>
           <t>Weighted average of our line size.</t>
         </is>
       </c>
-      <c r="D30" s="15" t="inlineStr">
+      <c r="D30" s="12" t="inlineStr">
         <is>
           <t>RBS</t>
         </is>
       </c>
-      <c r="E30" s="19" t="inlineStr">
+      <c r="E30" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F30" s="15" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="F30" s="12" t="n"/>
+      <c r="G30" s="26" t="inlineStr">
+        <is>
+          <t>Built - see tab 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="23.25" customHeight="1" s="23">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>SCM Share</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>How much of our premium sits on someone else's balance sheet.</t>
         </is>
       </c>
-      <c r="C31" s="15" t="inlineStr">
+      <c r="C31" s="12" t="inlineStr">
         <is>
           <t>1 minus our own balance sheet's share of premium.</t>
         </is>
       </c>
-      <c r="D31" s="15" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>RBS</t>
         </is>
       </c>
-      <c r="E31" s="19" t="inlineStr">
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F31" s="15" t="inlineStr"/>
+      <c r="F31" s="12" t="n"/>
+      <c r="G31" s="26" t="inlineStr">
+        <is>
+          <t>Built - see tab 8</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>LOOKING AT ONE UNDERWRITER</t>
         </is>
       </c>
-      <c r="B32" s="21" t="n"/>
-      <c r="C32" s="21" t="n"/>
-      <c r="D32" s="21" t="n"/>
-      <c r="E32" s="21" t="n"/>
-      <c r="F32" s="11" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="B32" s="18" t="n"/>
+      <c r="C32" s="18" t="n"/>
+      <c r="D32" s="18" t="n"/>
+      <c r="E32" s="18" t="n"/>
+      <c r="F32" s="17" t="n"/>
+      <c r="G32" s="25" t="n"/>
+    </row>
+    <row r="33" ht="23.25" customHeight="1" s="23">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t>Submissions / Q/S / B/Q by underwriter</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>One underwriter's own win-rate performance.</t>
         </is>
       </c>
-      <c r="C33" s="15" t="inlineStr">
+      <c r="C33" s="12" t="inlineStr">
         <is>
           <t>Same funnel formulas, grouped by underwriter name.</t>
         </is>
       </c>
-      <c r="D33" s="15" t="inlineStr">
+      <c r="D33" s="12" t="inlineStr">
         <is>
           <t>DSR</t>
         </is>
       </c>
-      <c r="E33" s="19" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F33" s="15" t="inlineStr">
+      <c r="F33" s="12" t="inlineStr">
         <is>
           <t>Subject to the name-spelling limitation in tab 3, Rule 5.</t>
         </is>
       </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="G33" s="27" t="inlineStr">
+        <is>
+          <t>Built - read note - see tab 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="23.25" customHeight="1" s="23">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>Book quality by underwriter</t>
         </is>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>GELR, Commission and Margin %, but for one underwriter's own book.</t>
         </is>
       </c>
-      <c r="C34" s="15" t="inlineStr">
+      <c r="C34" s="12" t="inlineStr">
         <is>
           <t>Same formulas as above, grouped by underwriter name.</t>
         </is>
       </c>
-      <c r="D34" s="15" t="inlineStr">
+      <c r="D34" s="12" t="inlineStr">
         <is>
           <t>RBS</t>
         </is>
       </c>
-      <c r="E34" s="19" t="inlineStr">
+      <c r="E34" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F34" s="15" t="inlineStr">
+      <c r="F34" s="12" t="inlineStr">
         <is>
           <t>Same name-spelling limitation.</t>
         </is>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="G34" s="27" t="inlineStr">
+        <is>
+          <t>Built - read note - see tab 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58.15" customHeight="1" s="23">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>Peer comparison</t>
         </is>
       </c>
-      <c r="B35" s="15" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>How one underwriter compares to their colleagues.</t>
         </is>
       </c>
-      <c r="C35" s="15" t="inlineStr">
+      <c r="C35" s="12" t="inlineStr">
         <is>
           <t>Their figure ÷ the middle (median) figure of their peer group.</t>
         </is>
       </c>
-      <c r="D35" s="15" t="inlineStr">
+      <c r="D35" s="12" t="inlineStr">
         <is>
           <t>DSR + RBS</t>
         </is>
       </c>
-      <c r="E35" s="20" t="inlineStr">
+      <c r="E35" s="14" t="inlineStr">
         <is>
           <t>Yes*</t>
         </is>
       </c>
-      <c r="F35" s="15" t="inlineStr">
+      <c r="F35" s="12" t="inlineStr">
         <is>
           <t>*Matt's build leaves out anyone who wrote nothing when working out the middle figure, so a zero doesn't unfairly drag it down — but still lists them elsewhere. We can copy this, but should decide it on purpose, not copy it by accident.</t>
         </is>
       </c>
+      <c r="G35" s="27" t="inlineStr">
+        <is>
+          <t>Built - read note - see tab 8</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>PRODUCTIVITY (stand-in headcount — see tab 1, point 5, before using these)</t>
         </is>
       </c>
-      <c r="B36" s="21" t="n"/>
-      <c r="C36" s="21" t="n"/>
-      <c r="D36" s="21" t="n"/>
-      <c r="E36" s="21" t="n"/>
-      <c r="F36" s="11" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="B36" s="18" t="n"/>
+      <c r="C36" s="18" t="n"/>
+      <c r="D36" s="18" t="n"/>
+      <c r="E36" s="18" t="n"/>
+      <c r="F36" s="17" t="n"/>
+      <c r="G36" s="25" t="n"/>
+    </row>
+    <row r="37" ht="34.9" customHeight="1" s="23">
+      <c r="A37" s="12" t="inlineStr">
         <is>
           <t>Roster underwriters</t>
         </is>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>Every different underwriter with at least one submission in the period, win or not — the broader stand-in for headcount.</t>
         </is>
       </c>
-      <c r="C37" s="15" t="inlineStr">
+      <c r="C37" s="12" t="inlineStr">
         <is>
           <t>Count distinct Producing Underwriters with any DSR row in scope.</t>
         </is>
       </c>
-      <c r="D37" s="15" t="inlineStr">
+      <c r="D37" s="12" t="inlineStr">
         <is>
           <t>DSR (stand-in)</t>
         </is>
       </c>
-      <c r="E37" s="20" t="inlineStr">
+      <c r="E37" s="14" t="inlineStr">
         <is>
           <t>Yes — stand-in only</t>
         </is>
       </c>
-      <c r="F37" s="15" t="inlineStr">
+      <c r="F37" s="12" t="inlineStr">
         <is>
           <t>NOT the same as true employed headcount. Misses non-selling leadership and anyone who hasn't submitted anything yet. Cannot be split by Role or Tenure.</t>
         </is>
       </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="G37" s="27" t="inlineStr">
+        <is>
+          <t>Built - stand-in - see tab 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="34.9" customHeight="1" s="23">
+      <c r="A38" s="12" t="inlineStr">
         <is>
           <t>Active underwriters</t>
         </is>
       </c>
-      <c r="B38" s="15" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>Every different underwriter who WON at least one deal — a stricter, smaller stand-in, built entirely from RBS.</t>
         </is>
       </c>
-      <c r="C38" s="15" t="inlineStr">
+      <c r="C38" s="12" t="inlineStr">
         <is>
           <t>Count distinct Producing Underwriters with a bound RBS row in scope.</t>
         </is>
       </c>
-      <c r="D38" s="15" t="inlineStr">
+      <c r="D38" s="12" t="inlineStr">
         <is>
           <t>RBS (stand-in)</t>
         </is>
       </c>
-      <c r="E38" s="20" t="inlineStr">
+      <c r="E38" s="14" t="inlineStr">
         <is>
           <t>Yes — stand-in only</t>
         </is>
       </c>
-      <c r="F38" s="15" t="inlineStr">
+      <c r="F38" s="12" t="inlineStr">
         <is>
           <t>Narrower than Roster underwriters, but the steadier one to lead with: it's built entirely from RBS, our source of truth for bound business (tab 3, Rule 6).</t>
         </is>
       </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="G38" s="27" t="inlineStr">
+        <is>
+          <t>Built - stand-in - see tab 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="58.15" customHeight="1" s="23">
+      <c r="A39" s="12" t="inlineStr">
         <is>
           <t>Premium per Active Underwriter</t>
         </is>
       </c>
-      <c r="B39" s="15" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>Our recommended default productivity figure.</t>
         </is>
       </c>
-      <c r="C39" s="15" t="inlineStr">
+      <c r="C39" s="12" t="inlineStr">
         <is>
           <t>Bound Premium ÷ Active underwriters.</t>
         </is>
       </c>
-      <c r="D39" s="15" t="inlineStr">
+      <c r="D39" s="12" t="inlineStr">
         <is>
           <t>RBS (stand-in)</t>
         </is>
       </c>
-      <c r="E39" s="20" t="inlineStr">
+      <c r="E39" s="14" t="inlineStr">
         <is>
           <t>Yes — stand-in only</t>
         </is>
       </c>
-      <c r="F39" s="15" t="inlineStr">
+      <c r="F39" s="12" t="inlineStr">
         <is>
           <t>Reads a little better than true per-head productivity, since anyone who never won anything is left out of the count entirely. Premium per Roster underwriter (using the broader DSR-based count) is available as a second, wider view.</t>
         </is>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="G39" s="27" t="inlineStr">
+        <is>
+          <t>Built - stand-in - see tab 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="23.25" customHeight="1" s="23">
+      <c r="A40" s="12" t="inlineStr">
         <is>
           <t>UW Margin per Active Underwriter</t>
         </is>
       </c>
-      <c r="B40" s="15" t="inlineStr">
+      <c r="B40" s="12" t="inlineStr">
         <is>
           <t>Same idea, adjusted for how profitable the business was.</t>
         </is>
       </c>
-      <c r="C40" s="15" t="inlineStr">
+      <c r="C40" s="12" t="inlineStr">
         <is>
           <t>(Bound Premium × UW Margin %) ÷ Active underwriters.</t>
         </is>
       </c>
-      <c r="D40" s="15" t="inlineStr">
+      <c r="D40" s="12" t="inlineStr">
         <is>
           <t>RBS (stand-in)</t>
         </is>
       </c>
-      <c r="E40" s="20" t="inlineStr">
+      <c r="E40" s="14" t="inlineStr">
         <is>
           <t>Yes — stand-in only</t>
         </is>
       </c>
-      <c r="F40" s="15" t="inlineStr">
+      <c r="F40" s="12" t="inlineStr">
         <is>
           <t>Same catches as the line above.</t>
+        </is>
+      </c>
+      <c r="G40" s="27" t="inlineStr">
+        <is>
+          <t>Built - stand-in - see tab 8</t>
         </is>
       </c>
     </row>
@@ -3030,13 +3441,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" style="23" min="1" max="1"/>
+    <col width="36" customWidth="1" style="23" min="2" max="3"/>
+    <col width="42" customWidth="1" style="23" min="4" max="4"/>
+    <col width="20" customWidth="1" style="23" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3046,7 +3457,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="30" customHeight="1" s="23">
       <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Metric</t>
@@ -3067,124 +3478,159 @@
           <t>Note / catch</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>Built? (17 Sep 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="34.9" customHeight="1" s="23">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>New vs. Renewal Mix</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>What share of our book is brand-new business vs. repeat clients.</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>Split premium and count by New / Renewal (using the agreed rule in tab 3 for when the two reports disagree).</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="D3" s="12" t="n"/>
+      <c r="E3" s="26" t="inlineStr">
+        <is>
+          <t>Built - see tab 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="23.25" customHeight="1" s="23">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Placement Mix</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>What share of our book is Open Market vs. Facility deals vs. Agreements.</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>Split premium by placement type.</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>Useful next to GELR and Margin %, since these placement types often make money very differently.</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="E4" s="26" t="inlineStr">
+        <is>
+          <t>Built - see tab 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="23.25" customHeight="1" s="23">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Broker Concentration</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>How much of our book sits with just a few brokers.</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>Top brokers' premium ÷ total premium.</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr"/>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="26" t="inlineStr">
+        <is>
+          <t>Built - see tab 8</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Average Policy Length</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>How long our policies typically run for.</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>Average of the policy length in months.</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t>Built - see tab 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="81.40000000000001" customHeight="1" s="23">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Renewal Premium Growth</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>Of the business that came up for renewal, how much premium came back?</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>This year's renewal premium ÷ last year's premium on that same business.</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>IMPORTANT: this is NOT a true retention rate. A policy that didn't renew at all still leaves a DSR row (now that DSR is in scope) but no RBS row, so we CAN now at least see that it existed and didn't come back — an improvement on the RBS-only version, but the dollar figure here still only covers renewals that did happen.</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="E7" s="27" t="inlineStr">
+        <is>
+          <t>Built - read note - see tab 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="23.25" customHeight="1" s="23">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Rate Adequacy double-check</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>A sanity check on our own Rate Adequacy number.</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>Compare it against RBS's own ready-made “Achieved Price” column.</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>If the two disagree by a lot, that's worth chasing down before we trust either one.</t>
+        </is>
+      </c>
+      <c r="E8" s="27" t="inlineStr">
+        <is>
+          <t>Built - read note - see tab 8</t>
         </is>
       </c>
     </row>
@@ -3203,22 +3649,25 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" style="23" min="1" max="1"/>
+    <col width="34" customWidth="1" style="23" min="2" max="2"/>
+    <col width="18" customWidth="1" style="23" min="3" max="3"/>
+    <col width="60" customWidth="1" style="23" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="17" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="23">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>Everything left here needs the HR file, or columns that don't exist in RBS at all — DSR does not help with any of it.</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
+      <c r="B1" s="18" t="n"/>
+      <c r="C1" s="18" t="n"/>
+      <c r="D1" s="17" t="n"/>
+    </row>
+    <row r="2" ht="30" customHeight="1" s="23">
       <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Metric (from Matt's build)</t>
@@ -3241,218 +3690,218 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>AGENCY REVENUE (the source columns don't exist anywhere)</t>
         </is>
       </c>
-      <c r="B3" s="8" t="n"/>
-      <c r="C3" s="8" t="n"/>
-      <c r="D3" s="8" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="B3" s="18" t="n"/>
+      <c r="C3" s="18" t="n"/>
+      <c r="D3" s="17" t="n"/>
+    </row>
+    <row r="4" ht="58.15" customHeight="1" s="23">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Agency Revenue</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>Fee income earned on top of the underwriting margin.</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>RBS — non-standard columns</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>Needs a “Total Fees” column that isn't in the standard RBS report, and isn't in the official list of RBS columns either — we checked directly. Someone must have used a special, one-off version of RBS to build this originally. DSR does not carry this information either, so bringing DSR in doesn't help here.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+    <row r="5" ht="23.25" customHeight="1" s="23">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Fee Yield</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>Fee income as a share of premium.</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>RBS — non-standard columns</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>Same missing columns as above.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+    <row r="6" ht="23.25" customHeight="1" s="23">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Syndicate Fees / SCM Fees</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>The two pieces that make up Agency Revenue.</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>RBS — non-standard columns</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Same missing columns.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+    <row r="7" ht="23.25" customHeight="1" s="23">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Agency Revenue per person</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>Fee income divided by headcount.</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>RBS (non-standard) + HR file</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>Needs both the missing fee columns AND real headcount from the HR file.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+    <row r="8" ht="23.25" customHeight="1" s="23">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Agency Revenue bridge</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>What drove the change in fee income per person.</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>RBS (non-standard) + HR file</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>Depends entirely on the missing fee columns.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>TRUE HEADCOUNT, ROLE AND TENURE (needs the HR file — DSR doesn't fully solve this)</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n"/>
-      <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="B9" s="18" t="n"/>
+      <c r="C9" s="18" t="n"/>
+      <c r="D9" s="17" t="n"/>
+    </row>
+    <row r="10" ht="46.5" customHeight="1" s="23">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>Real Heads (headcount)</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>The true average number of people employed as underwriters, including anyone who didn't submit or win anything that period.</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>HR file</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>Our best stand-ins (Roster underwriters, Active underwriters — see tab 4) only ever count people who actually did something in DSR or RBS. A non-selling manager, a brand-new joiner, or someone on long leave never appears in either stand-in, no matter how much DSR data we have.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+    <row r="11" ht="23.25" customHeight="1" s="23">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>True Premium / person, Margin / person, Revenue / person</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>Real productivity per employed person, not per active person.</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>DSR or RBS + HR file</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>All divide by real headcount, which we still don't have.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+    <row r="12" ht="23.25" customHeight="1" s="23">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Splitting figures by Role</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>Comparing underwriters vs. leadership.</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>HR file</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>Role is only recorded in the HR file. Neither DSR nor RBS records a person's job role.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Splitting figures by Tenure</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>Comparing newer vs. longer-serving staff.</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>HR file</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>Tenure (start date at the company) is only recorded in the HR file.</t>
         </is>
@@ -3466,4 +3915,4355 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" style="23" min="1" max="1"/>
+    <col width="34" customWidth="1" style="23" min="2" max="2"/>
+    <col width="24" customWidth="1" style="23" min="3" max="3"/>
+    <col width="13" customWidth="1" style="23" min="4" max="4"/>
+    <col width="14" customWidth="1" style="23" min="5" max="5"/>
+    <col width="48" customWidth="1" style="23" min="6" max="6"/>
+    <col width="16" customWidth="1" style="23" min="7" max="7"/>
+    <col width="30" customWidth="1" style="23" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="54" customHeight="1" s="23">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Every filter on the dashboard, compared with Matt's build. Each filter narrows EVERY figure on the page the same way, on both DSR and RBS (tab 3, Rule 1). Every figure is shown next to the same period one year earlier. Your choices live in the page address, so a filtered view can be bookmarked or sent to someone and opens exactly as it was.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>Green = done / safe to use</t>
+        </is>
+      </c>
+      <c r="C2" s="30" t="inlineStr">
+        <is>
+          <t>Amber = works, read the note</t>
+        </is>
+      </c>
+      <c r="E2" s="31" t="inlineStr">
+        <is>
+          <t>Red = not available / not built</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" s="23">
+      <c r="A3" s="32" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="B3" s="32" t="inlineStr">
+        <is>
+          <t>What it does</t>
+        </is>
+      </c>
+      <c r="C3" s="32" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+      <c r="D3" s="32" t="inlineStr">
+        <is>
+          <t>In Matt's build?</t>
+        </is>
+      </c>
+      <c r="E3" s="32" t="inlineStr">
+        <is>
+          <t>On our dashboard?</t>
+        </is>
+      </c>
+      <c r="F3" s="32" t="inlineStr">
+        <is>
+          <t>Note / catch</t>
+        </is>
+      </c>
+      <c r="G3" s="32" t="inlineStr">
+        <is>
+          <t>Opens on (default)</t>
+        </is>
+      </c>
+      <c r="H3" s="32" t="inlineStr">
+        <is>
+          <t>Where in the code</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="33" t="inlineStr">
+        <is>
+          <t>TIME WINDOW</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="n"/>
+      <c r="C4" s="18" t="n"/>
+      <c r="D4" s="18" t="n"/>
+      <c r="E4" s="18" t="n"/>
+      <c r="F4" s="18" t="n"/>
+      <c r="G4" s="18" t="n"/>
+      <c r="H4" s="17" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="34" t="inlineStr">
+        <is>
+          <t>Timeframe</t>
+        </is>
+      </c>
+      <c r="B5" s="35" t="inlineStr">
+        <is>
+          <t>Picks the kind of window: year-to-date, or the last twelve months.</t>
+        </is>
+      </c>
+      <c r="C5" s="35" t="inlineStr">
+        <is>
+          <t>YTD / TTM</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E5" s="36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F5" s="35" t="inlineStr">
+        <is>
+          <t>YTD = January to the last COMPLETE month (data as at 15 Sep 2026 -&gt; Jan-Aug). TTM = the twelve months ending with the last complete month (Sep 2025-Aug 2026). Under TTM the month bar is fixed.</t>
+        </is>
+      </c>
+      <c r="G5" s="35" t="inlineStr">
+        <is>
+          <t>YTD</t>
+        </is>
+      </c>
+      <c r="H5" s="35" t="inlineStr">
+        <is>
+          <t>Scope.ttm_end_month in scope/filter.py; server/filters.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="34" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>Which year to look at. Always compared with the year before, same months.</t>
+        </is>
+      </c>
+      <c r="C6" s="35" t="inlineStr">
+        <is>
+          <t>Every year in the data up to today (2021-2026)</t>
+        </is>
+      </c>
+      <c r="D6" s="37" t="inlineStr">
+        <is>
+          <t>No - fixed at 2026 vs 2025</t>
+        </is>
+      </c>
+      <c r="E6" s="36" t="inlineStr">
+        <is>
+          <t>Yes (new)</t>
+        </is>
+      </c>
+      <c r="F6" s="35" t="inlineStr">
+        <is>
+          <t>Our addition. Looking at a past year uses the same months, so 2024 YTD is Jan-Aug 2024 vs Jan-Aug 2023.</t>
+        </is>
+      </c>
+      <c r="G6" s="35" t="inlineStr">
+        <is>
+          <t>Latest year</t>
+        </is>
+      </c>
+      <c r="H6" s="35" t="inlineStr">
+        <is>
+          <t>Scope.year; scope/period.py prior_year_scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="34" t="inlineStr">
+        <is>
+          <t>Months</t>
+        </is>
+      </c>
+      <c r="B7" s="35" t="inlineStr">
+        <is>
+          <t>Tick the months to include, e.g. only Q1.</t>
+        </is>
+      </c>
+      <c r="C7" s="35" t="inlineStr">
+        <is>
+          <t>Jan-Dec, any mix</t>
+        </is>
+      </c>
+      <c r="D7" s="36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E7" s="36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F7" s="35" t="inlineStr">
+        <is>
+          <t>The month still in progress has an orange dot - its figures are incomplete. Unticking every month goes back to YTD.</t>
+        </is>
+      </c>
+      <c r="G7" s="35" t="inlineStr">
+        <is>
+          <t>Jan to last complete month</t>
+        </is>
+      </c>
+      <c r="H7" s="35" t="inlineStr">
+        <is>
+          <t>Scope.months</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="34" t="inlineStr">
+        <is>
+          <t>Date basis</t>
+        </is>
+      </c>
+      <c r="B8" s="35" t="inlineStr">
+        <is>
+          <t>Which date decides the month a policy belongs to.</t>
+        </is>
+      </c>
+      <c r="C8" s="35" t="inlineStr">
+        <is>
+          <t>Inception / Submission</t>
+        </is>
+      </c>
+      <c r="D8" s="36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E8" s="36" t="inlineStr">
+        <is>
+          <t>Yes - with a limit</t>
+        </is>
+      </c>
+      <c r="F8" s="35" t="inlineStr">
+        <is>
+          <t>Tab 3, Rule 3: RBS has no submission date. On Submission, only DSR-only figures are shown (Submissions, Quotes, Quote rate, Roster underwriters); everything needing RBS is blank with a note, rather than quietly mixing two different months. Matt's build mixes them.</t>
+        </is>
+      </c>
+      <c r="G8" s="35" t="inlineStr">
+        <is>
+          <t>Inception</t>
+        </is>
+      </c>
+      <c r="H8" s="35" t="inlineStr">
+        <is>
+          <t>Scope.date_basis; SUBMISSION_BASIS_NOTE in pipeline/build_dashboard_data.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="33" t="inlineStr">
+        <is>
+          <t>WHAT KIND OF BUSINESS</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="n"/>
+      <c r="C9" s="18" t="n"/>
+      <c r="D9" s="18" t="n"/>
+      <c r="E9" s="18" t="n"/>
+      <c r="F9" s="18" t="n"/>
+      <c r="G9" s="18" t="n"/>
+      <c r="H9" s="17" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="34" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="B10" s="35" t="inlineStr">
+        <is>
+          <t>New business, renewals, or both.</t>
+        </is>
+      </c>
+      <c r="C10" s="35" t="inlineStr">
+        <is>
+          <t>All / New / Renewal</t>
+        </is>
+      </c>
+      <c r="D10" s="36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E10" s="36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F10" s="35" t="inlineStr">
+        <is>
+          <t>Follows RBS's Renewal Status where DSR disagrees (tab 3, Rule 2). RARC and Renewal Premium Growth always look at renewals, whatever is picked here. Matt's build opens on New.</t>
+        </is>
+      </c>
+      <c r="G10" s="35" t="inlineStr">
+        <is>
+          <t>All (Matt: New)</t>
+        </is>
+      </c>
+      <c r="H10" s="35" t="inlineStr">
+        <is>
+          <t>Scope.business_type; DEFAULT_BUSINESS_TYPE in config/settings.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="34" t="inlineStr">
+        <is>
+          <t>Placement</t>
+        </is>
+      </c>
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>How the business reached us.</t>
+        </is>
+      </c>
+      <c r="C11" s="35" t="inlineStr">
+        <is>
+          <t>All / Open Market / Facility/DUA / Agreement</t>
+        </is>
+      </c>
+      <c r="D11" s="36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E11" s="36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F11" s="35" t="inlineStr">
+        <is>
+          <t>Our data also has Agreement business, which Matt's list doesn't show. Matt's build opens on Open Market because that's what his LOB workbook reconciles to - see tab 9.</t>
+        </is>
+      </c>
+      <c r="G11" s="35" t="inlineStr">
+        <is>
+          <t>All (Matt: Open Market)</t>
+        </is>
+      </c>
+      <c r="H11" s="35" t="inlineStr">
+        <is>
+          <t>Scope.placement; DEFAULT_PLACEMENT in config/settings.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="34" t="inlineStr">
+        <is>
+          <t>Line of business</t>
+        </is>
+      </c>
+      <c r="B12" s="35" t="inlineStr">
+        <is>
+          <t>One class of business, e.g. Cyber.</t>
+        </is>
+      </c>
+      <c r="C12" s="35" t="inlineStr">
+        <is>
+          <t>Dropdown, only what's in the other filters</t>
+        </is>
+      </c>
+      <c r="D12" s="36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E12" s="36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F12" s="35" t="inlineStr">
+        <is>
+          <t>Same values on DSR and RBS (tab 3, Rule 2).</t>
+        </is>
+      </c>
+      <c r="G12" s="35" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H12" s="35" t="inlineStr">
+        <is>
+          <t>Scope.line_of_business; scope/options.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="34" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="B13" s="35" t="inlineStr">
+        <is>
+          <t>One producing entity, e.g. Mosaic UK.</t>
+        </is>
+      </c>
+      <c r="C13" s="35" t="inlineStr">
+        <is>
+          <t>Dropdown, only what's in the other filters</t>
+        </is>
+      </c>
+      <c r="D13" s="36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E13" s="36" t="inlineStr">
+        <is>
+          <t>Yes - read the note</t>
+        </is>
+      </c>
+      <c r="F13" s="35" t="inlineStr">
+        <is>
+          <t>DSR's spellings mapped onto RBS's ("Mosaic Syndicate 2610" -&gt; "Mosaic 2610"). Our data has 12 entities, including syndicates (1609, 2610, 5399, 5431); Matt's list has 7 office entities, so he may group them - open question in tab 9.</t>
+        </is>
+      </c>
+      <c r="G13" s="35" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H13" s="35" t="inlineStr">
+        <is>
+          <t>Scope.entity; normalise_entity in config/field_map.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="34" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="B14" s="35" t="inlineStr">
+        <is>
+          <t>A product within a line, e.g. Cyber Tech, W&amp;I Tax.</t>
+        </is>
+      </c>
+      <c r="C14" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D14" s="36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E14" s="38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F14" s="35" t="inlineStr">
+        <is>
+          <t>Not in DSR or RBS. Matt's build takes it from a product roster and Lloyd's Risk Code mapping we don't have. Shown greyed out. Needs that mapping table - tab 9.</t>
+        </is>
+      </c>
+      <c r="G14" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="33" t="inlineStr">
+        <is>
+          <t>WHO WROTE IT</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="n"/>
+      <c r="C15" s="18" t="n"/>
+      <c r="D15" s="18" t="n"/>
+      <c r="E15" s="18" t="n"/>
+      <c r="F15" s="18" t="n"/>
+      <c r="G15" s="18" t="n"/>
+      <c r="H15" s="17" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="34" t="inlineStr">
+        <is>
+          <t>Underwriter</t>
+        </is>
+      </c>
+      <c r="B16" s="35" t="inlineStr">
+        <is>
+          <t>One underwriter. Also: click a name in the Underwriters table.</t>
+        </is>
+      </c>
+      <c r="C16" s="35" t="inlineStr">
+        <is>
+          <t>Dropdown, only what's in the other filters</t>
+        </is>
+      </c>
+      <c r="D16" s="36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E16" s="36" t="inlineStr">
+        <is>
+          <t>Yes - read the note</t>
+        </is>
+      </c>
+      <c r="F16" s="35" t="inlineStr">
+        <is>
+          <t>Names matched after tidying capitals, punctuation and spaces only (tab 3, Rule 5). Real duplicates seen: "Stedman, Rob" / "Stedman, Robert", "Hirst, Justin" / "Hurst, Justin". Picking a name keeps the peer comparison against everyone else in the other filters.</t>
+        </is>
+      </c>
+      <c r="G16" s="35" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H16" s="35" t="inlineStr">
+        <is>
+          <t>Scope.underwriter; ingest/underwriter_names.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="34" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="B17" s="35" t="inlineStr">
+        <is>
+          <t>Underwriters vs. leadership / UA.</t>
+        </is>
+      </c>
+      <c r="C17" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D17" s="36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E17" s="38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F17" s="35" t="inlineStr">
+        <is>
+          <t>Only in the HR file. Shown greyed out.</t>
+        </is>
+      </c>
+      <c r="G17" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" s="35" t="inlineStr">
+        <is>
+          <t>HR_AVAILABLE in config/settings.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="34" t="inlineStr">
+        <is>
+          <t>Tenure</t>
+        </is>
+      </c>
+      <c r="B18" s="35" t="inlineStr">
+        <is>
+          <t>Years at Mosaic: 0-1, 1-2, 2+.</t>
+        </is>
+      </c>
+      <c r="C18" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D18" s="36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E18" s="38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F18" s="35" t="inlineStr">
+        <is>
+          <t>Only in the HR file. Shown greyed out. Bands already in TENURE_BANDS.</t>
+        </is>
+      </c>
+      <c r="G18" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" s="35" t="inlineStr">
+        <is>
+          <t>TENURE_BANDS in config/settings.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="33" t="inlineStr">
+        <is>
+          <t>HOW THE FILTERS BEHAVE</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="n"/>
+      <c r="C19" s="18" t="n"/>
+      <c r="D19" s="18" t="n"/>
+      <c r="E19" s="18" t="n"/>
+      <c r="F19" s="18" t="n"/>
+      <c r="G19" s="18" t="n"/>
+      <c r="H19" s="17" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="34" t="inlineStr">
+        <is>
+          <t>Cascading dropdowns</t>
+        </is>
+      </c>
+      <c r="B20" s="35" t="inlineStr">
+        <is>
+          <t>Each dropdown only offers choices that exist under the other filters.</t>
+        </is>
+      </c>
+      <c r="C20" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D20" s="36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E20" s="36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F20" s="35" t="inlineStr">
+        <is>
+          <t>Built from both reports, this period and last year's. If a change makes a picked name impossible, it's cleared and the page says so, instead of showing an empty page.</t>
+        </is>
+      </c>
+      <c r="G20" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" s="35" t="inlineStr">
+        <is>
+          <t>scope/options.py; drop_stranded_selections in server/filters.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="34" t="inlineStr">
+        <is>
+          <t>Reset</t>
+        </is>
+      </c>
+      <c r="B21" s="35" t="inlineStr">
+        <is>
+          <t>Back to the defaults.</t>
+        </is>
+      </c>
+      <c r="C21" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D21" s="36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E21" s="36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F21" s="35" t="inlineStr">
+        <is>
+          <t>Defaults are one place: config/settings.py (DEFAULT_...).</t>
+        </is>
+      </c>
+      <c r="G21" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" s="35" t="inlineStr">
+        <is>
+          <t>server/filters.py default_state</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="34" t="inlineStr">
+        <is>
+          <t>Shareable address</t>
+        </is>
+      </c>
+      <c r="B22" s="35" t="inlineStr">
+        <is>
+          <t>The filters are in the page address.</t>
+        </is>
+      </c>
+      <c r="C22" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D22" s="37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E22" s="36" t="inlineStr">
+        <is>
+          <t>Yes (new)</t>
+        </is>
+      </c>
+      <c r="F22" s="35" t="inlineStr">
+        <is>
+          <t>Bookmark or paste a filtered view. A broken or old link falls back to defaults rather than showing wrong numbers.</t>
+        </is>
+      </c>
+      <c r="G22" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" s="35" t="inlineStr">
+        <is>
+          <t>FilterState.query in server/filters.py</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I68"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" style="23" min="1" max="1"/>
+    <col width="11" customWidth="1" style="23" min="2" max="2"/>
+    <col width="13" customWidth="1" style="23" min="3" max="3"/>
+    <col width="22" customWidth="1" style="23" min="4" max="4"/>
+    <col width="36" customWidth="1" style="23" min="5" max="5"/>
+    <col width="26" customWidth="1" style="23" min="6" max="6"/>
+    <col width="24" customWidth="1" style="23" min="7" max="7"/>
+    <col width="12" customWidth="1" style="23" min="8" max="8"/>
+    <col width="40" customWidth="1" style="23" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="54" customHeight="1" s="23">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Where every rule and metric stands in the code, so progress can be tracked. "Jan-Aug 2026" is what the dashboard shows on real data as at 15 Sep 2026, all filters off - use it to spot a figure that moves unexpectedly after a change. Last updated 17 Sep 2026. When you change a metric: update its row here, and its test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>Green = done / safe to use</t>
+        </is>
+      </c>
+      <c r="C2" s="30" t="inlineStr">
+        <is>
+          <t>Amber = works, read the note</t>
+        </is>
+      </c>
+      <c r="E2" s="31" t="inlineStr">
+        <is>
+          <t>Red = not available / not built</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" s="23">
+      <c r="A3" s="32" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B3" s="32" t="inlineStr">
+        <is>
+          <t>Workbook tab</t>
+        </is>
+      </c>
+      <c r="C3" s="32" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D3" s="32" t="inlineStr">
+        <is>
+          <t>On the dashboard</t>
+        </is>
+      </c>
+      <c r="E3" s="32" t="inlineStr">
+        <is>
+          <t>Code (file / function)</t>
+        </is>
+      </c>
+      <c r="F3" s="32" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="G3" s="32" t="inlineStr">
+        <is>
+          <t>Jan-Aug 2026 (vs 2025)</t>
+        </is>
+      </c>
+      <c r="H3" s="32" t="inlineStr">
+        <is>
+          <t>Last changed</t>
+        </is>
+      </c>
+      <c r="I3" s="32" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="33" t="inlineStr">
+        <is>
+          <t>MAKING DSR + RBS AGREE (tab 3)</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="n"/>
+      <c r="C4" s="18" t="n"/>
+      <c r="D4" s="18" t="n"/>
+      <c r="E4" s="18" t="n"/>
+      <c r="F4" s="18" t="n"/>
+      <c r="G4" s="18" t="n"/>
+      <c r="H4" s="18" t="n"/>
+      <c r="I4" s="17" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="34" t="inlineStr">
+        <is>
+          <t>Rule 1 - one shared filter</t>
+        </is>
+      </c>
+      <c r="B5" s="35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D5" s="35" t="inlineStr">
+        <is>
+          <t>Every figure</t>
+        </is>
+      </c>
+      <c r="E5" s="35" t="inlineStr">
+        <is>
+          <t>scope/filter.py apply_scope</t>
+        </is>
+      </c>
+      <c r="F5" s="35" t="inlineStr">
+        <is>
+          <t>test_scope.py</t>
+        </is>
+      </c>
+      <c r="G5" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H5" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="I5" s="35" t="inlineStr">
+        <is>
+          <t>Now also covers TTM, date basis and the filter speed-up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="34" t="inlineStr">
+        <is>
+          <t>Rule 2 - field name translation</t>
+        </is>
+      </c>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C6" s="36" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D6" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E6" s="35" t="inlineStr">
+        <is>
+          <t>config/field_map.py FIELD_MAP</t>
+        </is>
+      </c>
+      <c r="F6" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I6" s="35" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="34" t="inlineStr">
+        <is>
+          <t>Rule 2 - New vs Renewal follows RBS</t>
+        </is>
+      </c>
+      <c r="B7" s="35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C7" s="36" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D7" s="35" t="inlineStr">
+        <is>
+          <t>Business filter</t>
+        </is>
+      </c>
+      <c r="E7" s="35" t="inlineStr">
+        <is>
+          <t>ingest/align_reports.py</t>
+        </is>
+      </c>
+      <c r="F7" s="35" t="inlineStr">
+        <is>
+          <t>test_alignment.py</t>
+        </is>
+      </c>
+      <c r="G7" s="35" t="inlineStr">
+        <is>
+          <t>271 policies changed (all years)</t>
+        </is>
+      </c>
+      <c r="H7" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="I7" s="35" t="inlineStr">
+        <is>
+          <t>Made ~10x faster; same result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="34" t="inlineStr">
+        <is>
+          <t>Rule 2 - entity spellings</t>
+        </is>
+      </c>
+      <c r="B8" s="35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C8" s="36" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D8" s="35" t="inlineStr">
+        <is>
+          <t>Entity filter</t>
+        </is>
+      </c>
+      <c r="E8" s="35" t="inlineStr">
+        <is>
+          <t>config/field_map.py normalise_entity</t>
+        </is>
+      </c>
+      <c r="F8" s="35" t="inlineStr">
+        <is>
+          <t>test_alignment.py</t>
+        </is>
+      </c>
+      <c r="G8" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I8" s="35" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="34" t="inlineStr">
+        <is>
+          <t>Rule 2 - one list of won statuses</t>
+        </is>
+      </c>
+      <c r="B9" s="35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C9" s="36" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D9" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E9" s="35" t="inlineStr">
+        <is>
+          <t>config/settings.py BIND_STATUSES</t>
+        </is>
+      </c>
+      <c r="F9" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I9" s="35" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="34" t="inlineStr">
+        <is>
+          <t>Rule 3 - inception date when both reports</t>
+        </is>
+      </c>
+      <c r="B10" s="35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C10" s="36" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D10" s="35" t="inlineStr">
+        <is>
+          <t>Date basis filter</t>
+        </is>
+      </c>
+      <c r="E10" s="35" t="inlineStr">
+        <is>
+          <t>scope/filter.py; pipeline SUBMISSION_BASIS_NOTE</t>
+        </is>
+      </c>
+      <c r="F10" s="35" t="inlineStr">
+        <is>
+          <t>test_scope.py</t>
+        </is>
+      </c>
+      <c r="G10" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="I10" s="35" t="inlineStr">
+        <is>
+          <t>Submission basis shows DSR-only figures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="34" t="inlineStr">
+        <is>
+          <t>Rule 4 - sum lines first, count policies</t>
+        </is>
+      </c>
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C11" s="36" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D11" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E11" s="35" t="inlineStr">
+        <is>
+          <t>metrics/premium.py, metrics/funnel.py</t>
+        </is>
+      </c>
+      <c r="F11" s="35" t="inlineStr">
+        <is>
+          <t>test_new_metrics.py</t>
+        </is>
+      </c>
+      <c r="G11" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="I11" s="35" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="34" t="inlineStr">
+        <is>
+          <t>Rule 5 - underwriter name tidy-up</t>
+        </is>
+      </c>
+      <c r="B12" s="35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C12" s="36" t="inlineStr">
+        <is>
+          <t>Done - partial fix</t>
+        </is>
+      </c>
+      <c r="D12" s="35" t="inlineStr">
+        <is>
+          <t>Underwriter filter + table</t>
+        </is>
+      </c>
+      <c r="E12" s="35" t="inlineStr">
+        <is>
+          <t>ingest/underwriter_names.py</t>
+        </is>
+      </c>
+      <c r="F12" s="35" t="inlineStr">
+        <is>
+          <t>test_alignment.py</t>
+        </is>
+      </c>
+      <c r="G12" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="I12" s="35" t="inlineStr">
+        <is>
+          <t>Genuine spelling differences still split one person in two - tab 9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="34" t="inlineStr">
+        <is>
+          <t>Rule 6 - cross-check, RBS wins</t>
+        </is>
+      </c>
+      <c r="B13" s="35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C13" s="36" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D13" s="35" t="inlineStr">
+        <is>
+          <t>Red badge on Bound Premium / Binds</t>
+        </is>
+      </c>
+      <c r="E13" s="35" t="inlineStr">
+        <is>
+          <t>reconcile/cross_check.py</t>
+        </is>
+      </c>
+      <c r="F13" s="35" t="inlineStr">
+        <is>
+          <t>test_reconcile.py</t>
+        </is>
+      </c>
+      <c r="G13" s="35" t="inlineStr">
+        <is>
+          <t>Premium 9.1% apart, binds 3.4% apart</t>
+        </is>
+      </c>
+      <c r="H13" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I13" s="35" t="inlineStr">
+        <is>
+          <t>Gap above 2% - tab 9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="33" t="inlineStr">
+        <is>
+          <t>THE FUNNEL (tab 4)</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="n"/>
+      <c r="C14" s="18" t="n"/>
+      <c r="D14" s="18" t="n"/>
+      <c r="E14" s="18" t="n"/>
+      <c r="F14" s="18" t="n"/>
+      <c r="G14" s="18" t="n"/>
+      <c r="H14" s="18" t="n"/>
+      <c r="I14" s="17" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="34" t="inlineStr">
+        <is>
+          <t>Submissions</t>
+        </is>
+      </c>
+      <c r="B15" s="35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C15" s="36" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="D15" s="35" t="inlineStr">
+        <is>
+          <t>The funnel</t>
+        </is>
+      </c>
+      <c r="E15" s="35" t="inlineStr">
+        <is>
+          <t>metrics/funnel.py submissions</t>
+        </is>
+      </c>
+      <c r="F15" s="35" t="inlineStr">
+        <is>
+          <t>test_funnel.py</t>
+        </is>
+      </c>
+      <c r="G15" s="35" t="inlineStr">
+        <is>
+          <t>25,939 (2025: 23,176)</t>
+        </is>
+      </c>
+      <c r="H15" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I15" s="35" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="34" t="inlineStr">
+        <is>
+          <t>Quotes</t>
+        </is>
+      </c>
+      <c r="B16" s="35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C16" s="36" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="D16" s="35" t="inlineStr">
+        <is>
+          <t>The funnel</t>
+        </is>
+      </c>
+      <c r="E16" s="35" t="inlineStr">
+        <is>
+          <t>metrics/funnel.py quotes</t>
+        </is>
+      </c>
+      <c r="F16" s="35" t="inlineStr">
+        <is>
+          <t>test_underwriters.py</t>
+        </is>
+      </c>
+      <c r="G16" s="35" t="inlineStr">
+        <is>
+          <t>11,488 (2025: 9,837)</t>
+        </is>
+      </c>
+      <c r="H16" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I16" s="35" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="34" t="inlineStr">
+        <is>
+          <t>Binds</t>
+        </is>
+      </c>
+      <c r="B17" s="35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C17" s="36" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="D17" s="35" t="inlineStr">
+        <is>
+          <t>Headline + The funnel</t>
+        </is>
+      </c>
+      <c r="E17" s="35" t="inlineStr">
+        <is>
+          <t>metrics/funnel.py binds_from_rbs</t>
+        </is>
+      </c>
+      <c r="F17" s="35" t="inlineStr">
+        <is>
+          <t>test_funnel.py</t>
+        </is>
+      </c>
+      <c r="G17" s="35" t="inlineStr">
+        <is>
+          <t>5,034 (2025: 4,501)</t>
+        </is>
+      </c>
+      <c r="H17" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I17" s="35" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="34" t="inlineStr">
+        <is>
+          <t>Q/S</t>
+        </is>
+      </c>
+      <c r="B18" s="35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C18" s="36" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="D18" s="35" t="inlineStr">
+        <is>
+          <t>The funnel</t>
+        </is>
+      </c>
+      <c r="E18" s="35" t="inlineStr">
+        <is>
+          <t>metrics/funnel.py quote_rate</t>
+        </is>
+      </c>
+      <c r="F18" s="35" t="inlineStr">
+        <is>
+          <t>test_funnel.py</t>
+        </is>
+      </c>
+      <c r="G18" s="35" t="inlineStr">
+        <is>
+          <t>44.3% (2025: 42.4%)</t>
+        </is>
+      </c>
+      <c r="H18" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I18" s="35" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="34" t="inlineStr">
+        <is>
+          <t>B/Q</t>
+        </is>
+      </c>
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C19" s="36" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="D19" s="35" t="inlineStr">
+        <is>
+          <t>The funnel</t>
+        </is>
+      </c>
+      <c r="E19" s="35" t="inlineStr">
+        <is>
+          <t>metrics/funnel.py bind_rate</t>
+        </is>
+      </c>
+      <c r="F19" s="35" t="inlineStr">
+        <is>
+          <t>test_funnel.py</t>
+        </is>
+      </c>
+      <c r="G19" s="35" t="inlineStr">
+        <is>
+          <t>43.8% (2025: 45.8%)</t>
+        </is>
+      </c>
+      <c r="H19" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I19" s="35" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="34" t="inlineStr">
+        <is>
+          <t>B/S</t>
+        </is>
+      </c>
+      <c r="B20" s="35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C20" s="36" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="D20" s="35" t="inlineStr">
+        <is>
+          <t>The funnel</t>
+        </is>
+      </c>
+      <c r="E20" s="35" t="inlineStr">
+        <is>
+          <t>metrics/funnel.py end_to_end_win_rate</t>
+        </is>
+      </c>
+      <c r="F20" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G20" s="35" t="inlineStr">
+        <is>
+          <t>19.4% (2025: 19.4%)</t>
+        </is>
+      </c>
+      <c r="H20" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I20" s="35" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="33" t="inlineStr">
+        <is>
+          <t>HOW MUCH WE WROTE (tab 4)</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="n"/>
+      <c r="C21" s="18" t="n"/>
+      <c r="D21" s="18" t="n"/>
+      <c r="E21" s="18" t="n"/>
+      <c r="F21" s="18" t="n"/>
+      <c r="G21" s="18" t="n"/>
+      <c r="H21" s="18" t="n"/>
+      <c r="I21" s="17" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="34" t="inlineStr">
+        <is>
+          <t>Bound Premium</t>
+        </is>
+      </c>
+      <c r="B22" s="35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C22" s="36" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="D22" s="35" t="inlineStr">
+        <is>
+          <t>Headline + How much we wrote</t>
+        </is>
+      </c>
+      <c r="E22" s="35" t="inlineStr">
+        <is>
+          <t>metrics/premium.py bound_premium</t>
+        </is>
+      </c>
+      <c r="F22" s="35" t="inlineStr">
+        <is>
+          <t>test_new_metrics.py</t>
+        </is>
+      </c>
+      <c r="G22" s="35" t="inlineStr">
+        <is>
+          <t>$601.7M (2025: $535.6M)</t>
+        </is>
+      </c>
+      <c r="H22" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="I22" s="35" t="inlineStr">
+        <is>
+          <t>Moved out of the pipeline file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="34" t="inlineStr">
+        <is>
+          <t>Average Deal Size</t>
+        </is>
+      </c>
+      <c r="B23" s="35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C23" s="36" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="D23" s="35" t="inlineStr">
+        <is>
+          <t>How much we wrote</t>
+        </is>
+      </c>
+      <c r="E23" s="35" t="inlineStr">
+        <is>
+          <t>metrics/premium.py average_deal_size</t>
+        </is>
+      </c>
+      <c r="F23" s="35" t="inlineStr">
+        <is>
+          <t>test_new_metrics.py</t>
+        </is>
+      </c>
+      <c r="G23" s="35" t="inlineStr">
+        <is>
+          <t>$119.5k (2025: $119.0k)</t>
+        </is>
+      </c>
+      <c r="H23" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="I23" s="35" t="inlineStr">
+        <is>
+          <t>New.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="33" t="inlineStr">
+        <is>
+          <t>HOW GOOD THE BUSINESS IS (tab 4)</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="n"/>
+      <c r="C24" s="18" t="n"/>
+      <c r="D24" s="18" t="n"/>
+      <c r="E24" s="18" t="n"/>
+      <c r="F24" s="18" t="n"/>
+      <c r="G24" s="18" t="n"/>
+      <c r="H24" s="18" t="n"/>
+      <c r="I24" s="17" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="34" t="inlineStr">
+        <is>
+          <t>GELR - book version</t>
+        </is>
+      </c>
+      <c r="B25" s="35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C25" s="36" t="inlineStr">
+        <is>
+          <t>Built - read note</t>
+        </is>
+      </c>
+      <c r="D25" s="35" t="inlineStr">
+        <is>
+          <t>How good the business is</t>
+        </is>
+      </c>
+      <c r="E25" s="35" t="inlineStr">
+        <is>
+          <t>metrics/quality.py gelr_book_basis</t>
+        </is>
+      </c>
+      <c r="F25" s="35" t="inlineStr">
+        <is>
+          <t>test_quality.py</t>
+        </is>
+      </c>
+      <c r="G25" s="35" t="inlineStr">
+        <is>
+          <t>38.8% (2025: 39.8%)</t>
+        </is>
+      </c>
+      <c r="H25" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I25" s="35" t="inlineStr">
+        <is>
+          <t>Blank GELR counts as 0 - tab 9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="34" t="inlineStr">
+        <is>
+          <t>GELR - margin version</t>
+        </is>
+      </c>
+      <c r="B26" s="35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C26" s="36" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="D26" s="35" t="inlineStr">
+        <is>
+          <t>How good the business is</t>
+        </is>
+      </c>
+      <c r="E26" s="35" t="inlineStr">
+        <is>
+          <t>metrics/quality.py gelr_margin_basis</t>
+        </is>
+      </c>
+      <c r="F26" s="35" t="inlineStr">
+        <is>
+          <t>test_quality.py</t>
+        </is>
+      </c>
+      <c r="G26" s="35" t="inlineStr">
+        <is>
+          <t>39.0% (2025: 39.8%)</t>
+        </is>
+      </c>
+      <c r="H26" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I26" s="35" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="34" t="inlineStr">
+        <is>
+          <t>Commission - book version</t>
+        </is>
+      </c>
+      <c r="B27" s="35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C27" s="36" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="D27" s="35" t="inlineStr">
+        <is>
+          <t>How good the business is</t>
+        </is>
+      </c>
+      <c r="E27" s="35" t="inlineStr">
+        <is>
+          <t>metrics/quality.py commission_book_basis</t>
+        </is>
+      </c>
+      <c r="F27" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G27" s="35" t="inlineStr">
+        <is>
+          <t>16.6% (2025: 17.5%)</t>
+        </is>
+      </c>
+      <c r="H27" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I27" s="35" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="34" t="inlineStr">
+        <is>
+          <t>Commission - margin version</t>
+        </is>
+      </c>
+      <c r="B28" s="35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C28" s="36" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="D28" s="35" t="inlineStr">
+        <is>
+          <t>How good the business is</t>
+        </is>
+      </c>
+      <c r="E28" s="35" t="inlineStr">
+        <is>
+          <t>metrics/quality.py commission_margin_basis</t>
+        </is>
+      </c>
+      <c r="F28" s="35" t="inlineStr">
+        <is>
+          <t>test_quality.py</t>
+        </is>
+      </c>
+      <c r="G28" s="35" t="inlineStr">
+        <is>
+          <t>16.6% (2025: 17.5%)</t>
+        </is>
+      </c>
+      <c r="H28" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I28" s="35" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="34" t="inlineStr">
+        <is>
+          <t>UW Margin %</t>
+        </is>
+      </c>
+      <c r="B29" s="35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C29" s="36" t="inlineStr">
+        <is>
+          <t>Built - read note</t>
+        </is>
+      </c>
+      <c r="D29" s="35" t="inlineStr">
+        <is>
+          <t>Headline + How good the business is</t>
+        </is>
+      </c>
+      <c r="E29" s="35" t="inlineStr">
+        <is>
+          <t>metrics/quality.py uw_margin_pct</t>
+        </is>
+      </c>
+      <c r="F29" s="35" t="inlineStr">
+        <is>
+          <t>test_quality.py</t>
+        </is>
+      </c>
+      <c r="G29" s="35" t="inlineStr">
+        <is>
+          <t>44.4% (2025: 42.7%)</t>
+        </is>
+      </c>
+      <c r="H29" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I29" s="35" t="inlineStr">
+        <is>
+          <t>Internal commission not subtracted - tab 9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="34" t="inlineStr">
+        <is>
+          <t>Margin cover</t>
+        </is>
+      </c>
+      <c r="B30" s="35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C30" s="36" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="D30" s="35" t="inlineStr">
+        <is>
+          <t>How good the business is</t>
+        </is>
+      </c>
+      <c r="E30" s="35" t="inlineStr">
+        <is>
+          <t>metrics/quality.py margin_cover</t>
+        </is>
+      </c>
+      <c r="F30" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G30" s="35" t="inlineStr">
+        <is>
+          <t>99.5% (2025: 100.0%)</t>
+        </is>
+      </c>
+      <c r="H30" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I30" s="35" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="34" t="inlineStr">
+        <is>
+          <t>Commission cover</t>
+        </is>
+      </c>
+      <c r="B31" s="35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C31" s="36" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="D31" s="35" t="inlineStr">
+        <is>
+          <t>How good the business is</t>
+        </is>
+      </c>
+      <c r="E31" s="35" t="inlineStr">
+        <is>
+          <t>metrics/quality.py commission_cover</t>
+        </is>
+      </c>
+      <c r="F31" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G31" s="35" t="inlineStr">
+        <is>
+          <t>88.5% (2025: 89.4%)</t>
+        </is>
+      </c>
+      <c r="H31" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I31" s="35" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="34" t="inlineStr">
+        <is>
+          <t>Attachment point (Excess)</t>
+        </is>
+      </c>
+      <c r="B32" s="35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C32" s="36" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="D32" s="35" t="inlineStr">
+        <is>
+          <t>How good the business is</t>
+        </is>
+      </c>
+      <c r="E32" s="35" t="inlineStr">
+        <is>
+          <t>metrics/quality.py attachment_point_excess</t>
+        </is>
+      </c>
+      <c r="F32" s="35" t="inlineStr">
+        <is>
+          <t>test_new_metrics.py</t>
+        </is>
+      </c>
+      <c r="G32" s="35" t="inlineStr">
+        <is>
+          <t>$30.0M (2025: $30.0M)</t>
+        </is>
+      </c>
+      <c r="H32" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="I32" s="35" t="inlineStr">
+        <is>
+          <t>New. Median; blank Excess left out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="34" t="inlineStr">
+        <is>
+          <t>Attachment point (Primary)</t>
+        </is>
+      </c>
+      <c r="B33" s="35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C33" s="36" t="inlineStr">
+        <is>
+          <t>Built - read note</t>
+        </is>
+      </c>
+      <c r="D33" s="35" t="inlineStr">
+        <is>
+          <t>How good the business is</t>
+        </is>
+      </c>
+      <c r="E33" s="35" t="inlineStr">
+        <is>
+          <t>metrics/quality.py attachment_point_primary</t>
+        </is>
+      </c>
+      <c r="F33" s="35" t="inlineStr">
+        <is>
+          <t>test_new_metrics.py</t>
+        </is>
+      </c>
+      <c r="G33" s="35" t="inlineStr">
+        <is>
+          <t>$29.3k (2025: $25.0k)</t>
+        </is>
+      </c>
+      <c r="H33" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="I33" s="35" t="inlineStr">
+        <is>
+          <t>New. Blank deductible = 0, so understated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="34" t="inlineStr">
+        <is>
+          <t>Average Limit (shown as Median limit)</t>
+        </is>
+      </c>
+      <c r="B34" s="35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C34" s="36" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="D34" s="35" t="inlineStr">
+        <is>
+          <t>How good the business is</t>
+        </is>
+      </c>
+      <c r="E34" s="35" t="inlineStr">
+        <is>
+          <t>metrics/quality.py median_limit</t>
+        </is>
+      </c>
+      <c r="F34" s="35" t="inlineStr">
+        <is>
+          <t>test_new_metrics.py</t>
+        </is>
+      </c>
+      <c r="G34" s="35" t="inlineStr">
+        <is>
+          <t>$5.85M (2025: $7.28M)</t>
+        </is>
+      </c>
+      <c r="H34" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="I34" s="35" t="inlineStr">
+        <is>
+          <t>New. Named as a median, as the workbook asks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="33" t="inlineStr">
+        <is>
+          <t>PRICING (tab 4)</t>
+        </is>
+      </c>
+      <c r="B35" s="18" t="n"/>
+      <c r="C35" s="18" t="n"/>
+      <c r="D35" s="18" t="n"/>
+      <c r="E35" s="18" t="n"/>
+      <c r="F35" s="18" t="n"/>
+      <c r="G35" s="18" t="n"/>
+      <c r="H35" s="18" t="n"/>
+      <c r="I35" s="17" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="34" t="inlineStr">
+        <is>
+          <t>Rate Adequacy</t>
+        </is>
+      </c>
+      <c r="B36" s="35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C36" s="36" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="D36" s="35" t="inlineStr">
+        <is>
+          <t>Pricing</t>
+        </is>
+      </c>
+      <c r="E36" s="35" t="inlineStr">
+        <is>
+          <t>metrics/quality.py rate_adequacy</t>
+        </is>
+      </c>
+      <c r="F36" s="35" t="inlineStr">
+        <is>
+          <t>test_quality.py</t>
+        </is>
+      </c>
+      <c r="G36" s="35" t="inlineStr">
+        <is>
+          <t>139.7% (2025: 131.8%)</t>
+        </is>
+      </c>
+      <c r="H36" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I36" s="35" t="inlineStr">
+        <is>
+          <t>Same rows on both sides (fixes Matt's overstatement).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="34" t="inlineStr">
+        <is>
+          <t>RARC</t>
+        </is>
+      </c>
+      <c r="B37" s="35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C37" s="36" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="D37" s="35" t="inlineStr">
+        <is>
+          <t>Pricing</t>
+        </is>
+      </c>
+      <c r="E37" s="35" t="inlineStr">
+        <is>
+          <t>metrics/quality.py rarc</t>
+        </is>
+      </c>
+      <c r="F37" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G37" s="35" t="inlineStr">
+        <is>
+          <t>99.5% (2025: 95.4%)</t>
+        </is>
+      </c>
+      <c r="H37" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I37" s="35" t="inlineStr">
+        <is>
+          <t>Renewals only. No test yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="33" t="inlineStr">
+        <is>
+          <t>WHAT KIND OF BOOK WE WRITE (tab 4)</t>
+        </is>
+      </c>
+      <c r="B38" s="18" t="n"/>
+      <c r="C38" s="18" t="n"/>
+      <c r="D38" s="18" t="n"/>
+      <c r="E38" s="18" t="n"/>
+      <c r="F38" s="18" t="n"/>
+      <c r="G38" s="18" t="n"/>
+      <c r="H38" s="18" t="n"/>
+      <c r="I38" s="17" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="34" t="inlineStr">
+        <is>
+          <t>Mosaic as Lead</t>
+        </is>
+      </c>
+      <c r="B39" s="35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C39" s="36" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="D39" s="35" t="inlineStr">
+        <is>
+          <t>What kind of book</t>
+        </is>
+      </c>
+      <c r="E39" s="35" t="inlineStr">
+        <is>
+          <t>metrics/composition.py mosaic_as_lead</t>
+        </is>
+      </c>
+      <c r="F39" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G39" s="35" t="inlineStr">
+        <is>
+          <t>68.1% (2025: 63.9%)</t>
+        </is>
+      </c>
+      <c r="H39" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I39" s="35" t="inlineStr">
+        <is>
+          <t>Row count, not premium.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="34" t="inlineStr">
+        <is>
+          <t>Primary Share</t>
+        </is>
+      </c>
+      <c r="B40" s="35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C40" s="36" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="D40" s="35" t="inlineStr">
+        <is>
+          <t>What kind of book</t>
+        </is>
+      </c>
+      <c r="E40" s="35" t="inlineStr">
+        <is>
+          <t>metrics/composition.py primary_share</t>
+        </is>
+      </c>
+      <c r="F40" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G40" s="35" t="inlineStr">
+        <is>
+          <t>52.0% (2025: 52.3%)</t>
+        </is>
+      </c>
+      <c r="H40" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I40" s="35" t="inlineStr">
+        <is>
+          <t>Row count, not premium.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="34" t="inlineStr">
+        <is>
+          <t>Average Agency Share</t>
+        </is>
+      </c>
+      <c r="B41" s="35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C41" s="36" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="D41" s="35" t="inlineStr">
+        <is>
+          <t>What kind of book</t>
+        </is>
+      </c>
+      <c r="E41" s="35" t="inlineStr">
+        <is>
+          <t>metrics/composition.py average_agency_share</t>
+        </is>
+      </c>
+      <c r="F41" s="35" t="inlineStr">
+        <is>
+          <t>test_new_metrics.py</t>
+        </is>
+      </c>
+      <c r="G41" s="35" t="inlineStr">
+        <is>
+          <t>59.3% (2025: 60.2%)</t>
+        </is>
+      </c>
+      <c r="H41" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="I41" s="35" t="inlineStr">
+        <is>
+          <t>New. Premium-weighted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="34" t="inlineStr">
+        <is>
+          <t>SCM Share</t>
+        </is>
+      </c>
+      <c r="B42" s="35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C42" s="36" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="D42" s="35" t="inlineStr">
+        <is>
+          <t>What kind of book</t>
+        </is>
+      </c>
+      <c r="E42" s="35" t="inlineStr">
+        <is>
+          <t>metrics/composition.py scm_share</t>
+        </is>
+      </c>
+      <c r="F42" s="35" t="inlineStr">
+        <is>
+          <t>test_new_metrics.py</t>
+        </is>
+      </c>
+      <c r="G42" s="35" t="inlineStr">
+        <is>
+          <t>64.7% (2025: 52.5%)</t>
+        </is>
+      </c>
+      <c r="H42" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="I42" s="35" t="inlineStr">
+        <is>
+          <t>New. 1 - Mosaic 1609 premium / all agency premium.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="33" t="inlineStr">
+        <is>
+          <t>LOOKING AT ONE UNDERWRITER (tab 4)</t>
+        </is>
+      </c>
+      <c r="B43" s="18" t="n"/>
+      <c r="C43" s="18" t="n"/>
+      <c r="D43" s="18" t="n"/>
+      <c r="E43" s="18" t="n"/>
+      <c r="F43" s="18" t="n"/>
+      <c r="G43" s="18" t="n"/>
+      <c r="H43" s="18" t="n"/>
+      <c r="I43" s="17" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="34" t="inlineStr">
+        <is>
+          <t>Funnel by underwriter</t>
+        </is>
+      </c>
+      <c r="B44" s="35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C44" s="36" t="inlineStr">
+        <is>
+          <t>Built - read note</t>
+        </is>
+      </c>
+      <c r="D44" s="35" t="inlineStr">
+        <is>
+          <t>Underwriters table + Underwriter filter</t>
+        </is>
+      </c>
+      <c r="E44" s="35" t="inlineStr">
+        <is>
+          <t>metrics/underwriters.py underwriter_table</t>
+        </is>
+      </c>
+      <c r="F44" s="35" t="inlineStr">
+        <is>
+          <t>test_underwriters.py</t>
+        </is>
+      </c>
+      <c r="G44" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H44" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="I44" s="35" t="inlineStr">
+        <is>
+          <t>New. Name catch, Rule 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="34" t="inlineStr">
+        <is>
+          <t>Book quality by underwriter</t>
+        </is>
+      </c>
+      <c r="B45" s="35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C45" s="36" t="inlineStr">
+        <is>
+          <t>Built - read note</t>
+        </is>
+      </c>
+      <c r="D45" s="35" t="inlineStr">
+        <is>
+          <t>Underwriters table (UW Margin %)</t>
+        </is>
+      </c>
+      <c r="E45" s="35" t="inlineStr">
+        <is>
+          <t>metrics/underwriters.py underwriter_table</t>
+        </is>
+      </c>
+      <c r="F45" s="35" t="inlineStr">
+        <is>
+          <t>test_underwriters.py</t>
+        </is>
+      </c>
+      <c r="G45" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H45" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="I45" s="35" t="inlineStr">
+        <is>
+          <t>New. Margin only; GELR and Commission per underwriter show when you filter to one name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="34" t="inlineStr">
+        <is>
+          <t>Peer comparison</t>
+        </is>
+      </c>
+      <c r="B46" s="35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C46" s="36" t="inlineStr">
+        <is>
+          <t>Built - read note</t>
+        </is>
+      </c>
+      <c r="D46" s="35" t="inlineStr">
+        <is>
+          <t>Underwriters table (vs peer median)</t>
+        </is>
+      </c>
+      <c r="E46" s="35" t="inlineStr">
+        <is>
+          <t>metrics/underwriters.py; PEER_MEDIAN_EXCLUDES_ZERO_PREMIUM</t>
+        </is>
+      </c>
+      <c r="F46" s="35" t="inlineStr">
+        <is>
+          <t>test_underwriters.py</t>
+        </is>
+      </c>
+      <c r="G46" s="35" t="inlineStr">
+        <is>
+          <t>Peer median $3.24M</t>
+        </is>
+      </c>
+      <c r="H46" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="I46" s="35" t="inlineStr">
+        <is>
+          <t>New. Zero-premium underwriters left out of the median, as Matt does - tab 9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="33" t="inlineStr">
+        <is>
+          <t>PRODUCTIVITY - STAND-IN HEADCOUNT (tab 4)</t>
+        </is>
+      </c>
+      <c r="B47" s="18" t="n"/>
+      <c r="C47" s="18" t="n"/>
+      <c r="D47" s="18" t="n"/>
+      <c r="E47" s="18" t="n"/>
+      <c r="F47" s="18" t="n"/>
+      <c r="G47" s="18" t="n"/>
+      <c r="H47" s="18" t="n"/>
+      <c r="I47" s="17" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="34" t="inlineStr">
+        <is>
+          <t>Roster underwriters</t>
+        </is>
+      </c>
+      <c r="B48" s="35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C48" s="36" t="inlineStr">
+        <is>
+          <t>Built - stand-in</t>
+        </is>
+      </c>
+      <c r="D48" s="35" t="inlineStr">
+        <is>
+          <t>Productivity</t>
+        </is>
+      </c>
+      <c r="E48" s="35" t="inlineStr">
+        <is>
+          <t>metrics/headcount.py roster_underwriters</t>
+        </is>
+      </c>
+      <c r="F48" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G48" s="35" t="inlineStr">
+        <is>
+          <t>146 (2025: 112)</t>
+        </is>
+      </c>
+      <c r="H48" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I48" s="35" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="34" t="inlineStr">
+        <is>
+          <t>Active underwriters</t>
+        </is>
+      </c>
+      <c r="B49" s="35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C49" s="36" t="inlineStr">
+        <is>
+          <t>Built - stand-in</t>
+        </is>
+      </c>
+      <c r="D49" s="35" t="inlineStr">
+        <is>
+          <t>Productivity</t>
+        </is>
+      </c>
+      <c r="E49" s="35" t="inlineStr">
+        <is>
+          <t>metrics/headcount.py active_underwriters</t>
+        </is>
+      </c>
+      <c r="F49" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G49" s="35" t="inlineStr">
+        <is>
+          <t>135 (2025: 109)</t>
+        </is>
+      </c>
+      <c r="H49" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I49" s="35" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="34" t="inlineStr">
+        <is>
+          <t>Premium per Active Underwriter</t>
+        </is>
+      </c>
+      <c r="B50" s="35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C50" s="36" t="inlineStr">
+        <is>
+          <t>Built - stand-in</t>
+        </is>
+      </c>
+      <c r="D50" s="35" t="inlineStr">
+        <is>
+          <t>Headline + Productivity</t>
+        </is>
+      </c>
+      <c r="E50" s="35" t="inlineStr">
+        <is>
+          <t>metrics/headcount.py premium_per_active_underwriter</t>
+        </is>
+      </c>
+      <c r="F50" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G50" s="35" t="inlineStr">
+        <is>
+          <t>$4.46M (2025: $4.91M)</t>
+        </is>
+      </c>
+      <c r="H50" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I50" s="35" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="34" t="inlineStr">
+        <is>
+          <t>Premium per Roster Underwriter</t>
+        </is>
+      </c>
+      <c r="B51" s="35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C51" s="36" t="inlineStr">
+        <is>
+          <t>Built - stand-in</t>
+        </is>
+      </c>
+      <c r="D51" s="35" t="inlineStr">
+        <is>
+          <t>Productivity</t>
+        </is>
+      </c>
+      <c r="E51" s="35" t="inlineStr">
+        <is>
+          <t>metrics/headcount.py premium_per_roster_underwriter</t>
+        </is>
+      </c>
+      <c r="F51" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G51" s="35" t="inlineStr">
+        <is>
+          <t>$4.12M (2025: $4.78M)</t>
+        </is>
+      </c>
+      <c r="H51" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I51" s="35" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="34" t="inlineStr">
+        <is>
+          <t>UW Margin per Active Underwriter</t>
+        </is>
+      </c>
+      <c r="B52" s="35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C52" s="36" t="inlineStr">
+        <is>
+          <t>Built - stand-in</t>
+        </is>
+      </c>
+      <c r="D52" s="35" t="inlineStr">
+        <is>
+          <t>Productivity</t>
+        </is>
+      </c>
+      <c r="E52" s="35" t="inlineStr">
+        <is>
+          <t>metrics/headcount.py uw_margin_per_active_underwriter</t>
+        </is>
+      </c>
+      <c r="F52" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G52" s="35" t="inlineStr">
+        <is>
+          <t>$1.98M (2025: $2.10M)</t>
+        </is>
+      </c>
+      <c r="H52" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I52" s="35" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="33" t="inlineStr">
+        <is>
+          <t>NEW IDEAS (tab 5)</t>
+        </is>
+      </c>
+      <c r="B53" s="18" t="n"/>
+      <c r="C53" s="18" t="n"/>
+      <c r="D53" s="18" t="n"/>
+      <c r="E53" s="18" t="n"/>
+      <c r="F53" s="18" t="n"/>
+      <c r="G53" s="18" t="n"/>
+      <c r="H53" s="18" t="n"/>
+      <c r="I53" s="17" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="34" t="inlineStr">
+        <is>
+          <t>New vs. Renewal Mix</t>
+        </is>
+      </c>
+      <c r="B54" s="35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C54" s="36" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="D54" s="35" t="inlineStr">
+        <is>
+          <t>Mix bar</t>
+        </is>
+      </c>
+      <c r="E54" s="35" t="inlineStr">
+        <is>
+          <t>metrics/composition.py new_vs_renewal_mix</t>
+        </is>
+      </c>
+      <c r="F54" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G54" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H54" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I54" s="35" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="34" t="inlineStr">
+        <is>
+          <t>Placement Mix</t>
+        </is>
+      </c>
+      <c r="B55" s="35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C55" s="36" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="D55" s="35" t="inlineStr">
+        <is>
+          <t>Mix bar</t>
+        </is>
+      </c>
+      <c r="E55" s="35" t="inlineStr">
+        <is>
+          <t>metrics/composition.py placement_mix</t>
+        </is>
+      </c>
+      <c r="F55" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G55" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H55" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I55" s="35" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="34" t="inlineStr">
+        <is>
+          <t>Broker Concentration</t>
+        </is>
+      </c>
+      <c r="B56" s="35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C56" s="36" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="D56" s="35" t="inlineStr">
+        <is>
+          <t>What kind of book</t>
+        </is>
+      </c>
+      <c r="E56" s="35" t="inlineStr">
+        <is>
+          <t>metrics/composition.py broker_concentration</t>
+        </is>
+      </c>
+      <c r="F56" s="35" t="inlineStr">
+        <is>
+          <t>test_new_metrics.py</t>
+        </is>
+      </c>
+      <c r="G56" s="35" t="inlineStr">
+        <is>
+          <t>23.6% (2025: 27.8%)</t>
+        </is>
+      </c>
+      <c r="H56" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="I56" s="35" t="inlineStr">
+        <is>
+          <t>New. Top 5 - BROKER_CONCENTRATION_TOP_N.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="34" t="inlineStr">
+        <is>
+          <t>Average Policy Length</t>
+        </is>
+      </c>
+      <c r="B57" s="35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C57" s="36" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="D57" s="35" t="inlineStr">
+        <is>
+          <t>What kind of book</t>
+        </is>
+      </c>
+      <c r="E57" s="35" t="inlineStr">
+        <is>
+          <t>metrics/composition.py average_policy_length</t>
+        </is>
+      </c>
+      <c r="F57" s="35" t="inlineStr">
+        <is>
+          <t>test_new_metrics.py</t>
+        </is>
+      </c>
+      <c r="G57" s="35" t="inlineStr">
+        <is>
+          <t>18.3 mo (2025: 19.5 mo)</t>
+        </is>
+      </c>
+      <c r="H57" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="I57" s="35" t="inlineStr">
+        <is>
+          <t>New. Once per policy, not per line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="34" t="inlineStr">
+        <is>
+          <t>Renewal Premium Growth</t>
+        </is>
+      </c>
+      <c r="B58" s="35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C58" s="36" t="inlineStr">
+        <is>
+          <t>Built - read note</t>
+        </is>
+      </c>
+      <c r="D58" s="35" t="inlineStr">
+        <is>
+          <t>What kind of book</t>
+        </is>
+      </c>
+      <c r="E58" s="35" t="inlineStr">
+        <is>
+          <t>metrics/composition.py renewal_premium_growth</t>
+        </is>
+      </c>
+      <c r="F58" s="35" t="inlineStr">
+        <is>
+          <t>test_new_metrics.py</t>
+        </is>
+      </c>
+      <c r="G58" s="35" t="inlineStr">
+        <is>
+          <t>92.6% (2025: 105.5%)</t>
+        </is>
+      </c>
+      <c r="H58" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="I58" s="35" t="inlineStr">
+        <is>
+          <t>New. Not a true retention rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="34" t="inlineStr">
+        <is>
+          <t>Rate Adequacy double-check</t>
+        </is>
+      </c>
+      <c r="B59" s="35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C59" s="36" t="inlineStr">
+        <is>
+          <t>Built - read note</t>
+        </is>
+      </c>
+      <c r="D59" s="35" t="inlineStr">
+        <is>
+          <t>Pricing</t>
+        </is>
+      </c>
+      <c r="E59" s="35" t="inlineStr">
+        <is>
+          <t>metrics/quality.py rate_adequacy_rbs_benchmark</t>
+        </is>
+      </c>
+      <c r="F59" s="35" t="inlineStr">
+        <is>
+          <t>test_new_metrics.py</t>
+        </is>
+      </c>
+      <c r="G59" s="35" t="inlineStr">
+        <is>
+          <t>139.4% (2025: 131.7%)</t>
+        </is>
+      </c>
+      <c r="H59" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="I59" s="35" t="inlineStr">
+        <is>
+          <t>New. Uses RBS's benchmark premium, not the Achieved Price column - tab 9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="33" t="inlineStr">
+        <is>
+          <t>CAN'T BUILD (tab 6)</t>
+        </is>
+      </c>
+      <c r="B60" s="18" t="n"/>
+      <c r="C60" s="18" t="n"/>
+      <c r="D60" s="18" t="n"/>
+      <c r="E60" s="18" t="n"/>
+      <c r="F60" s="18" t="n"/>
+      <c r="G60" s="18" t="n"/>
+      <c r="H60" s="18" t="n"/>
+      <c r="I60" s="17" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="34" t="inlineStr">
+        <is>
+          <t>Agency Revenue, Fee Yield, fees</t>
+        </is>
+      </c>
+      <c r="B61" s="35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C61" s="38" t="inlineStr">
+        <is>
+          <t>Can't build</t>
+        </is>
+      </c>
+      <c r="D61" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E61" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F61" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G61" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H61" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I61" s="35" t="inlineStr">
+        <is>
+          <t>Fee columns don't exist in the standard RBS report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="34" t="inlineStr">
+        <is>
+          <t>True headcount, Role, Tenure</t>
+        </is>
+      </c>
+      <c r="B62" s="35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C62" s="38" t="inlineStr">
+        <is>
+          <t>Can't build</t>
+        </is>
+      </c>
+      <c r="D62" s="35" t="inlineStr">
+        <is>
+          <t>Greyed-out filters</t>
+        </is>
+      </c>
+      <c r="E62" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F62" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G62" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H62" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I62" s="35" t="inlineStr">
+        <is>
+          <t>Needs the HR file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="34" t="inlineStr">
+        <is>
+          <t>Product filter</t>
+        </is>
+      </c>
+      <c r="B63" s="35" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C63" s="38" t="inlineStr">
+        <is>
+          <t>Can't build</t>
+        </is>
+      </c>
+      <c r="D63" s="35" t="inlineStr">
+        <is>
+          <t>Greyed-out filter</t>
+        </is>
+      </c>
+      <c r="E63" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F63" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G63" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H63" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I63" s="35" t="inlineStr">
+        <is>
+          <t>Needs Matt's product mapping - tab 9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="33" t="inlineStr">
+        <is>
+          <t>THE DASHBOARD ITSELF</t>
+        </is>
+      </c>
+      <c r="B64" s="18" t="n"/>
+      <c r="C64" s="18" t="n"/>
+      <c r="D64" s="18" t="n"/>
+      <c r="E64" s="18" t="n"/>
+      <c r="F64" s="18" t="n"/>
+      <c r="G64" s="18" t="n"/>
+      <c r="H64" s="18" t="n"/>
+      <c r="I64" s="17" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="34" t="inlineStr">
+        <is>
+          <t>Filter bar</t>
+        </is>
+      </c>
+      <c r="B65" s="35" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C65" s="36" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="D65" s="35" t="inlineStr">
+        <is>
+          <t>Top of page</t>
+        </is>
+      </c>
+      <c r="E65" s="35" t="inlineStr">
+        <is>
+          <t>server/filters.py, scope/options.py</t>
+        </is>
+      </c>
+      <c r="F65" s="35" t="inlineStr">
+        <is>
+          <t>test_filters.py</t>
+        </is>
+      </c>
+      <c r="G65" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H65" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="I65" s="35" t="inlineStr">
+        <is>
+          <t>New.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="34" t="inlineStr">
+        <is>
+          <t>Same period last year, with change</t>
+        </is>
+      </c>
+      <c r="B66" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C66" s="36" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="D66" s="35" t="inlineStr">
+        <is>
+          <t>Every figure</t>
+        </is>
+      </c>
+      <c r="E66" s="35" t="inlineStr">
+        <is>
+          <t>compute_with_comparison in pipeline/build_dashboard_data.py</t>
+        </is>
+      </c>
+      <c r="F66" s="35" t="inlineStr">
+        <is>
+          <t>test_filters.py</t>
+        </is>
+      </c>
+      <c r="G66" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H66" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="I66" s="35" t="inlineStr">
+        <is>
+          <t>New. Change coloured green/red where higher or lower is clearly better.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="34" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="B67" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C67" s="36" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D67" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E67" s="35" t="inlineStr">
+        <is>
+          <t>pipeline prepare(); add_filter_columns in scope/filter.py</t>
+        </is>
+      </c>
+      <c r="F67" s="35" t="inlineStr">
+        <is>
+          <t>test_scope.py</t>
+        </is>
+      </c>
+      <c r="G67" s="35" t="inlineStr">
+        <is>
+          <t>~1-2s per new filter choice, instant repeat</t>
+        </is>
+      </c>
+      <c r="H67" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="I67" s="35" t="inlineStr">
+        <is>
+          <t>Was ~5s. Data is cleaned once per refresh, not per click.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="34" t="inlineStr">
+        <is>
+          <t>Page renders for every view</t>
+        </is>
+      </c>
+      <c r="B68" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C68" s="36" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D68" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E68" s="35" t="inlineStr">
+        <is>
+          <t>server/dashboard.py</t>
+        </is>
+      </c>
+      <c r="F68" s="35" t="inlineStr">
+        <is>
+          <t>test_filters.py</t>
+        </is>
+      </c>
+      <c r="G68" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H68" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="I68" s="35" t="inlineStr">
+        <is>
+          <t>Catches a figure the page asks for that the pipeline stopped producing.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A64:I64"/>
+    <mergeCell ref="A43:I43"/>
+    <mergeCell ref="A47:I47"/>
+    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A60:I60"/>
+    <mergeCell ref="A14:I14"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A53:I53"/>
+    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A38:I38"/>
+    <mergeCell ref="A24:I24"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" style="23" min="1" max="1"/>
+    <col width="34" customWidth="1" style="23" min="2" max="2"/>
+    <col width="40" customWidth="1" style="23" min="3" max="3"/>
+    <col width="32" customWidth="1" style="23" min="4" max="4"/>
+    <col width="11" customWidth="1" style="23" min="5" max="5"/>
+    <col width="18" customWidth="1" style="23" min="6" max="6"/>
+    <col width="11" customWidth="1" style="23" min="7" max="7"/>
+    <col width="30" customWidth="1" style="23" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="54" customHeight="1" s="23">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Every judgement call behind the numbers, in one list: what the dashboard does today, and whether that's agreed or still needs someone to decide. Open = worth raising. Decided = settled, with the reason. When something is decided, change Status, fill in the date, and update the setting or code named in the last column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>Green = done / safe to use</t>
+        </is>
+      </c>
+      <c r="C2" s="30" t="inlineStr">
+        <is>
+          <t>Amber = works, read the note</t>
+        </is>
+      </c>
+      <c r="E2" s="31" t="inlineStr">
+        <is>
+          <t>Red = not available / not built</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" s="23">
+      <c r="A3" s="32" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="32" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="C3" s="32" t="inlineStr">
+        <is>
+          <t>What the dashboard does today</t>
+        </is>
+      </c>
+      <c r="D3" s="32" t="inlineStr">
+        <is>
+          <t>Other options</t>
+        </is>
+      </c>
+      <c r="E3" s="32" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F3" s="32" t="inlineStr">
+        <is>
+          <t>Who can decide</t>
+        </is>
+      </c>
+      <c r="G3" s="32" t="inlineStr">
+        <is>
+          <t>Raised</t>
+        </is>
+      </c>
+      <c r="H3" s="32" t="inlineStr">
+        <is>
+          <t>Where to change it</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="33" t="inlineStr">
+        <is>
+          <t>OPEN - WORTH RAISING</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="n"/>
+      <c r="C4" s="18" t="n"/>
+      <c r="D4" s="18" t="n"/>
+      <c r="E4" s="18" t="n"/>
+      <c r="F4" s="18" t="n"/>
+      <c r="G4" s="18" t="n"/>
+      <c r="H4" s="17" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="35" t="inlineStr">
+        <is>
+          <t>GELR book version: should a row with no GELR count as 0, or be left out?</t>
+        </is>
+      </c>
+      <c r="C5" s="35" t="inlineStr">
+        <is>
+          <t>Counts as 0 (reading tab 4's "across all rows" literally). Makes GELR look slightly better (40.55% vs 40.63% margin version, all years).</t>
+        </is>
+      </c>
+      <c r="D5" s="35" t="inlineStr">
+        <is>
+          <t>Leave blank rows out - then the book and margin versions are the same number.</t>
+        </is>
+      </c>
+      <c r="E5" s="37" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F5" s="35" t="inlineStr">
+        <is>
+          <t>Matt / Finance</t>
+        </is>
+      </c>
+      <c r="G5" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H5" s="35" t="inlineStr">
+        <is>
+          <t>metrics/quality.py gelr_book_basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>UW Margin %: should Mosaic's own internal commission also be subtracted?</t>
+        </is>
+      </c>
+      <c r="C6" s="35" t="inlineStr">
+        <is>
+          <t>Not subtracted: 100 - GELR - Commission.</t>
+        </is>
+      </c>
+      <c r="D6" s="35" t="inlineStr">
+        <is>
+          <t>Also subtract Mosaic 1609 Agency Commission.</t>
+        </is>
+      </c>
+      <c r="E6" s="37" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F6" s="35" t="inlineStr">
+        <is>
+          <t>Matt / Finance</t>
+        </is>
+      </c>
+      <c r="G6" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H6" s="35" t="inlineStr">
+        <is>
+          <t>metrics/quality.py uw_margin_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="35" t="inlineStr">
+        <is>
+          <t>Why do DSR and RBS disagree by more than "a percent or two"?</t>
+        </is>
+      </c>
+      <c r="C7" s="35" t="inlineStr">
+        <is>
+          <t>Keeps RBS's figure, shows a red badge. Jan-Aug 2026: premium 9.1% apart, binds 3.4% apart (all years: 11.9% and 3.7%).</t>
+        </is>
+      </c>
+      <c r="D7" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E7" s="37" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F7" s="35" t="inlineStr">
+        <is>
+          <t>Owners of the DSR and RBS extracts</t>
+        </is>
+      </c>
+      <c r="G7" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H7" s="35" t="inlineStr">
+        <is>
+          <t>reconcile/cross_check.py; RECONCILIATION_TOLERANCE_PCT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="35" t="inlineStr">
+        <is>
+          <t>Should rates built on very few deals be hidden or flagged?</t>
+        </is>
+      </c>
+      <c r="C8" s="35" t="inlineStr">
+        <is>
+          <t>Always shown (tab 4: blank only when there's nothing to divide by). An underwriter with 2 submissions can show 50%.</t>
+        </is>
+      </c>
+      <c r="D8" s="35" t="inlineStr">
+        <is>
+          <t>Hide below a minimum; or show a "small sample" marker.</t>
+        </is>
+      </c>
+      <c r="E8" s="37" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F8" s="35" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="G8" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H8" s="35" t="inlineStr">
+        <is>
+          <t>metrics/funnel.py; metrics/underwriters.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="35" t="inlineStr">
+        <is>
+          <t>Which filters should the dashboard open on?</t>
+        </is>
+      </c>
+      <c r="C9" s="35" t="inlineStr">
+        <is>
+          <t>Everything (All business, All placement), YTD, inception date.</t>
+        </is>
+      </c>
+      <c r="D9" s="35" t="inlineStr">
+        <is>
+          <t>Match Matt: New + Open Market, which his LOB workbook reconciles to.</t>
+        </is>
+      </c>
+      <c r="E9" s="37" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F9" s="35" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="G9" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H9" s="35" t="inlineStr">
+        <is>
+          <t>DEFAULT_... in config/settings.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="35" t="inlineStr">
+        <is>
+          <t>Product filter: where does Matt's product list (Cyber Tech, W&amp;I Tax, ...) come from?</t>
+        </is>
+      </c>
+      <c r="C10" s="35" t="inlineStr">
+        <is>
+          <t>Filter greyed out.</t>
+        </is>
+      </c>
+      <c r="D10" s="35" t="inlineStr">
+        <is>
+          <t>Get the product roster / Lloyd's Risk Code mapping and add a product column in ingest/.</t>
+        </is>
+      </c>
+      <c r="E10" s="37" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F10" s="35" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="G10" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H10" s="35" t="inlineStr">
+        <is>
+          <t>ingest/clean_rbs.py, ingest/clean_dsr.py, scope/filter.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>Entities: our data has 12 (incl. syndicates 1609, 2610, 5399, 5431, SP, Asta Europe); Matt's list has 7 offices. Does he group them?</t>
+        </is>
+      </c>
+      <c r="C11" s="35" t="inlineStr">
+        <is>
+          <t>Shows all 12 as they appear in the reports.</t>
+        </is>
+      </c>
+      <c r="D11" s="35" t="inlineStr">
+        <is>
+          <t>Add a grouping (e.g. syndicate -&gt; office) to ENTITY_ALIASES.</t>
+        </is>
+      </c>
+      <c r="E11" s="37" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F11" s="35" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="G11" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H11" s="35" t="inlineStr">
+        <is>
+          <t>config/field_map.py ENTITY_ALIASES</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="35" t="inlineStr">
+        <is>
+          <t>Underwriter names spelled two ways - build a manual list?</t>
+        </is>
+      </c>
+      <c r="C12" s="35" t="inlineStr">
+        <is>
+          <t>Tidies capitals, punctuation and spaces only. Seen in the real data: "Stedman, Rob" / "Stedman, Robert", "Hirst, Justin" / "Hurst, Justin".</t>
+        </is>
+      </c>
+      <c r="D12" s="35" t="inlineStr">
+        <is>
+          <t>A short hand-made alias list, checked by someone who knows the team.</t>
+        </is>
+      </c>
+      <c r="E12" s="37" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F12" s="35" t="inlineStr">
+        <is>
+          <t>UW team lead</t>
+        </is>
+      </c>
+      <c r="G12" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H12" s="35" t="inlineStr">
+        <is>
+          <t>ingest/underwriter_names.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="35" t="inlineStr">
+        <is>
+          <t>RBS's "Achieved Price (%)" column: what unit is it in?</t>
+        </is>
+      </c>
+      <c r="C13" s="35" t="inlineStr">
+        <is>
+          <t>Not used. The Rate Adequacy double-check uses RBS's own benchmark premium instead (Mosaic 1609 premium / 1609 benchmark premium).</t>
+        </is>
+      </c>
+      <c r="D13" s="35" t="inlineStr">
+        <is>
+          <t>Use Achieved Price once its unit is known (median ~1.3 after scaling, outliers in the hundreds of thousands).</t>
+        </is>
+      </c>
+      <c r="E13" s="37" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F13" s="35" t="inlineStr">
+        <is>
+          <t>RBS extract owner</t>
+        </is>
+      </c>
+      <c r="G13" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H13" s="35" t="inlineStr">
+        <is>
+          <t>metrics/quality.py rate_adequacy_rbs_benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="35" t="inlineStr">
+        <is>
+          <t>Peer median: leave out underwriters with no premium?</t>
+        </is>
+      </c>
+      <c r="C14" s="35" t="inlineStr">
+        <is>
+          <t>Left out, as in Matt's build, so a zero doesn't drag the middle figure down.</t>
+        </is>
+      </c>
+      <c r="D14" s="35" t="inlineStr">
+        <is>
+          <t>Include them (median falls).</t>
+        </is>
+      </c>
+      <c r="E14" s="37" t="inlineStr">
+        <is>
+          <t>Open - confirm</t>
+        </is>
+      </c>
+      <c r="F14" s="35" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="G14" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H14" s="35" t="inlineStr">
+        <is>
+          <t>PEER_MEDIAN_EXCLUDES_ZERO_PREMIUM in config/settings.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="33" t="inlineStr">
+        <is>
+          <t>DECIDED - WITH THE REASON</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="n"/>
+      <c r="C15" s="18" t="n"/>
+      <c r="D15" s="18" t="n"/>
+      <c r="E15" s="18" t="n"/>
+      <c r="F15" s="18" t="n"/>
+      <c r="G15" s="18" t="n"/>
+      <c r="H15" s="17" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="35" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="35" t="inlineStr">
+        <is>
+          <t>Submission date basis with RBS figures?</t>
+        </is>
+      </c>
+      <c r="C16" s="35" t="inlineStr">
+        <is>
+          <t>Only DSR-only figures shown; the rest blank with a note.</t>
+        </is>
+      </c>
+      <c r="D16" s="35" t="inlineStr">
+        <is>
+          <t>Matt's build mixes submission-month DSR with inception-month RBS.</t>
+        </is>
+      </c>
+      <c r="E16" s="36" t="inlineStr">
+        <is>
+          <t>Decided</t>
+        </is>
+      </c>
+      <c r="F16" s="35" t="inlineStr">
+        <is>
+          <t>Tab 3, Rule 3</t>
+        </is>
+      </c>
+      <c r="G16" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H16" s="35" t="inlineStr">
+        <is>
+          <t>pipeline/build_dashboard_data.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="35" t="inlineStr">
+        <is>
+          <t>Rate Adequacy: all premium vs benchmark from some rows?</t>
+        </is>
+      </c>
+      <c r="C17" s="35" t="inlineStr">
+        <is>
+          <t>Same rows on both sides (129.0% vs Matt-style 129.2%, all years).</t>
+        </is>
+      </c>
+      <c r="D17" s="35" t="inlineStr">
+        <is>
+          <t>Matt's version overstates.</t>
+        </is>
+      </c>
+      <c r="E17" s="36" t="inlineStr">
+        <is>
+          <t>Decided</t>
+        </is>
+      </c>
+      <c r="F17" s="35" t="inlineStr">
+        <is>
+          <t>Tab 4 note</t>
+        </is>
+      </c>
+      <c r="G17" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H17" s="35" t="inlineStr">
+        <is>
+          <t>metrics/quality.py rate_adequacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="35" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="35" t="inlineStr">
+        <is>
+          <t>Peer group when one underwriter is picked?</t>
+        </is>
+      </c>
+      <c r="C18" s="35" t="inlineStr">
+        <is>
+          <t>Everyone in the other filters - the picked underwriter is highlighted among them.</t>
+        </is>
+      </c>
+      <c r="D18" s="35" t="inlineStr">
+        <is>
+          <t>Only themselves (always reads 1.0x).</t>
+        </is>
+      </c>
+      <c r="E18" s="36" t="inlineStr">
+        <is>
+          <t>Decided</t>
+        </is>
+      </c>
+      <c r="F18" s="35" t="inlineStr">
+        <is>
+          <t>Common sense</t>
+        </is>
+      </c>
+      <c r="G18" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H18" s="35" t="inlineStr">
+        <is>
+          <t>pipeline/build_dashboard_data.py (underwriters)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>Average Policy Length: per line or per policy?</t>
+        </is>
+      </c>
+      <c r="C19" s="35" t="inlineStr">
+        <is>
+          <t>Once per policy (18.3 months Jan-Aug 2026).</t>
+        </is>
+      </c>
+      <c r="D19" s="35" t="inlineStr">
+        <is>
+          <t>Per line counts long multi-line policies several times.</t>
+        </is>
+      </c>
+      <c r="E19" s="36" t="inlineStr">
+        <is>
+          <t>Decided</t>
+        </is>
+      </c>
+      <c r="F19" s="35" t="inlineStr">
+        <is>
+          <t>Tab 3, Rule 4</t>
+        </is>
+      </c>
+      <c r="G19" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H19" s="35" t="inlineStr">
+        <is>
+          <t>metrics/composition.py average_policy_length</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="35" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="35" t="inlineStr">
+        <is>
+          <t>Renewal Premium Growth with the Business filter on New?</t>
+        </is>
+      </c>
+      <c r="C20" s="35" t="inlineStr">
+        <is>
+          <t>Still looks at renewals only, like RARC.</t>
+        </is>
+      </c>
+      <c r="D20" s="35" t="inlineStr">
+        <is>
+          <t>Blank on New.</t>
+        </is>
+      </c>
+      <c r="E20" s="36" t="inlineStr">
+        <is>
+          <t>Decided</t>
+        </is>
+      </c>
+      <c r="F20" s="35" t="inlineStr">
+        <is>
+          <t>Same rule as RARC (tab 4)</t>
+        </is>
+      </c>
+      <c r="G20" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H20" s="35" t="inlineStr">
+        <is>
+          <t>metrics/composition.py renewal_premium_growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="35" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="35" t="inlineStr">
+        <is>
+          <t>Attachment points: blank values?</t>
+        </is>
+      </c>
+      <c r="C21" s="35" t="inlineStr">
+        <is>
+          <t>Excess: blank left out. Primary: blank deductible = 0 (workbook note, same as Matt).</t>
+        </is>
+      </c>
+      <c r="D21" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E21" s="36" t="inlineStr">
+        <is>
+          <t>Decided</t>
+        </is>
+      </c>
+      <c r="F21" s="35" t="inlineStr">
+        <is>
+          <t>Tab 4 note</t>
+        </is>
+      </c>
+      <c r="G21" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H21" s="35" t="inlineStr">
+        <is>
+          <t>metrics/quality.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="35" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="35" t="inlineStr">
+        <is>
+          <t>SCM Share definition</t>
+        </is>
+      </c>
+      <c r="C22" s="35" t="inlineStr">
+        <is>
+          <t>1 - (Mosaic 1609 share of premium / all agency premium), as Matt.</t>
+        </is>
+      </c>
+      <c r="D22" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E22" s="36" t="inlineStr">
+        <is>
+          <t>Decided</t>
+        </is>
+      </c>
+      <c r="F22" s="35" t="inlineStr">
+        <is>
+          <t>Matt's build</t>
+        </is>
+      </c>
+      <c r="G22" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H22" s="35" t="inlineStr">
+        <is>
+          <t>metrics/composition.py scm_share</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="35" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="35" t="inlineStr">
+        <is>
+          <t>Timeframe: when is a month "complete"?</t>
+        </is>
+      </c>
+      <c r="C23" s="35" t="inlineStr">
+        <is>
+          <t>Data runs to the latest DSR submission date. A month is complete once that date reaches its last day (15 Sep 2026 -&gt; Aug is the last complete month).</t>
+        </is>
+      </c>
+      <c r="D23" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E23" s="36" t="inlineStr">
+        <is>
+          <t>Decided</t>
+        </is>
+      </c>
+      <c r="F23" s="35" t="inlineStr">
+        <is>
+          <t>Same as Matt</t>
+        </is>
+      </c>
+      <c r="G23" s="35" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H23" s="35" t="inlineStr">
+        <is>
+          <t>scope/period.py</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>